--- a/research/traditional_assets/database/data/taiwan/taiwan_beverage_soft.xlsx
+++ b/research/traditional_assets/database/data/taiwan/taiwan_beverage_soft.xlsx
@@ -1406,7 +1406,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1543,22 +1543,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07946791842877481</v>
+        <v>0.07934498259191726</v>
       </c>
       <c r="C2">
-        <v>546.9702094372589</v>
+        <v>543.2833812373898</v>
       </c>
       <c r="D2">
-        <v>511.6702094372588</v>
+        <v>513.5453812373898</v>
       </c>
       <c r="E2">
-        <v>-52.3</v>
+        <v>-46.73800000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>5.561999999999999</v>
       </c>
       <c r="G2">
         <v>35.3</v>
@@ -1579,28 +1579,28 @@
         <v>23.2</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2797686</v>
       </c>
       <c r="N2">
-        <v>23.2</v>
+        <v>22.9202314</v>
       </c>
       <c r="O2">
-        <v>4.64</v>
+        <v>4.58404628</v>
       </c>
       <c r="P2">
-        <v>18.56</v>
+        <v>18.33618512</v>
       </c>
       <c r="Q2">
-        <v>28.66</v>
+        <v>28.43618512</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07946791842877481</v>
+        <v>0.07973998241607805</v>
       </c>
       <c r="T2">
-        <v>0.6562503962404382</v>
+        <v>0.6615534297454115</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>82.92567500427138</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1625,22 +1625,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07934498259191726</v>
+        <v>0.0792220467550597</v>
       </c>
       <c r="C3">
-        <v>543.2833812373898</v>
+        <v>539.6103478727798</v>
       </c>
       <c r="D3">
-        <v>513.5453812373898</v>
+        <v>515.4343478727799</v>
       </c>
       <c r="E3">
-        <v>-46.73800000000001</v>
+        <v>-41.176</v>
       </c>
       <c r="F3">
-        <v>5.561999999999999</v>
+        <v>11.124</v>
       </c>
       <c r="G3">
         <v>35.3</v>
@@ -1661,28 +1661,28 @@
         <v>23.2</v>
       </c>
       <c r="M3">
-        <v>0.2797686</v>
+        <v>0.5595372</v>
       </c>
       <c r="N3">
-        <v>22.9202314</v>
+        <v>22.6404628</v>
       </c>
       <c r="O3">
-        <v>4.58404628</v>
+        <v>4.52809256</v>
       </c>
       <c r="P3">
-        <v>18.33618512</v>
+        <v>18.11237024</v>
       </c>
       <c r="Q3">
-        <v>28.43618512</v>
+        <v>28.21237023999999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07973998241607805</v>
+        <v>0.08001759872965276</v>
       </c>
       <c r="T3">
-        <v>0.6615534297454115</v>
+        <v>0.6669646884239556</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>82.92567500427138</v>
+        <v>41.46283750213569</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1707,22 +1707,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0792220467550597</v>
+        <v>0.07909911091820215</v>
       </c>
       <c r="C4">
-        <v>539.6103478727798</v>
+        <v>535.9512621294552</v>
       </c>
       <c r="D4">
-        <v>515.4343478727799</v>
+        <v>517.3372621294553</v>
       </c>
       <c r="E4">
-        <v>-41.176</v>
+        <v>-35.614</v>
       </c>
       <c r="F4">
-        <v>11.124</v>
+        <v>16.686</v>
       </c>
       <c r="G4">
         <v>35.3</v>
@@ -1743,28 +1743,28 @@
         <v>23.2</v>
       </c>
       <c r="M4">
-        <v>0.5595372</v>
+        <v>0.8393057999999998</v>
       </c>
       <c r="N4">
-        <v>22.6404628</v>
+        <v>22.3606942</v>
       </c>
       <c r="O4">
-        <v>4.52809256</v>
+        <v>4.47213884</v>
       </c>
       <c r="P4">
-        <v>18.11237024</v>
+        <v>17.88855536</v>
       </c>
       <c r="Q4">
-        <v>28.21237023999999</v>
+        <v>27.98855536</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08001759872965276</v>
+        <v>0.08030093909093006</v>
       </c>
       <c r="T4">
-        <v>0.6669646884239556</v>
+        <v>0.6724875194463872</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>41.46283750213569</v>
+        <v>27.64189166809047</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1789,22 +1789,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07909911091820215</v>
+        <v>0.07897617508134462</v>
       </c>
       <c r="C5">
-        <v>535.9512621294552</v>
+        <v>532.3062790580652</v>
       </c>
       <c r="D5">
-        <v>517.3372621294553</v>
+        <v>519.2542790580653</v>
       </c>
       <c r="E5">
-        <v>-35.614</v>
+        <v>-30.05200000000001</v>
       </c>
       <c r="F5">
-        <v>16.686</v>
+        <v>22.248</v>
       </c>
       <c r="G5">
         <v>35.3</v>
@@ -1825,28 +1825,28 @@
         <v>23.2</v>
       </c>
       <c r="M5">
-        <v>0.8393057999999998</v>
+        <v>1.1190744</v>
       </c>
       <c r="N5">
-        <v>22.3606942</v>
+        <v>22.0809256</v>
       </c>
       <c r="O5">
-        <v>4.47213884</v>
+        <v>4.416185120000001</v>
       </c>
       <c r="P5">
-        <v>17.88855536</v>
+        <v>17.66474048</v>
       </c>
       <c r="Q5">
-        <v>27.98855536</v>
+        <v>27.76474048</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08030093909093006</v>
+        <v>0.08059018237640064</v>
       </c>
       <c r="T5">
-        <v>0.6724875194463872</v>
+        <v>0.6781254094484529</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>27.64189166809047</v>
+        <v>20.73141875106785</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1871,22 +1871,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07897617508134462</v>
+        <v>0.07885323924448706</v>
       </c>
       <c r="C6">
-        <v>532.3062790580652</v>
+        <v>528.6755560159968</v>
       </c>
       <c r="D6">
-        <v>519.2542790580653</v>
+        <v>521.1855560159968</v>
       </c>
       <c r="E6">
-        <v>-30.05200000000001</v>
+        <v>-24.49000000000001</v>
       </c>
       <c r="F6">
-        <v>22.248</v>
+        <v>27.81</v>
       </c>
       <c r="G6">
         <v>35.3</v>
@@ -1907,28 +1907,28 @@
         <v>23.2</v>
       </c>
       <c r="M6">
-        <v>1.1190744</v>
+        <v>1.398843</v>
       </c>
       <c r="N6">
-        <v>22.0809256</v>
+        <v>21.801157</v>
       </c>
       <c r="O6">
-        <v>4.416185120000001</v>
+        <v>4.3602314</v>
       </c>
       <c r="P6">
-        <v>17.66474048</v>
+        <v>17.4409256</v>
       </c>
       <c r="Q6">
-        <v>27.76474048</v>
+        <v>27.5409256</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08059018237640064</v>
+        <v>0.08088551499419691</v>
       </c>
       <c r="T6">
-        <v>0.6781254094484529</v>
+        <v>0.6838819918716146</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>20.73141875106785</v>
+        <v>16.58513500085428</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1953,22 +1953,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07885323924448706</v>
+        <v>0.0787303034076295</v>
       </c>
       <c r="C7">
-        <v>528.6755560159968</v>
+        <v>525.0592527104296</v>
       </c>
       <c r="D7">
-        <v>521.1855560159968</v>
+        <v>523.1312527104296</v>
       </c>
       <c r="E7">
-        <v>-24.49000000000001</v>
+        <v>-18.928</v>
       </c>
       <c r="F7">
-        <v>27.81</v>
+        <v>33.372</v>
       </c>
       <c r="G7">
         <v>35.3</v>
@@ -1989,28 +1989,28 @@
         <v>23.2</v>
       </c>
       <c r="M7">
-        <v>1.398843</v>
+        <v>1.6786116</v>
       </c>
       <c r="N7">
-        <v>21.801157</v>
+        <v>21.5213884</v>
       </c>
       <c r="O7">
-        <v>4.3602314</v>
+        <v>4.30427768</v>
       </c>
       <c r="P7">
-        <v>17.4409256</v>
+        <v>17.21711072</v>
       </c>
       <c r="Q7">
-        <v>27.5409256</v>
+        <v>27.31711072</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08088551499419691</v>
+        <v>0.08118713128471225</v>
       </c>
       <c r="T7">
-        <v>0.6838819918716146</v>
+        <v>0.6897610547718649</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>16.58513500085428</v>
+        <v>13.82094583404523</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2035,22 +2035,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.0787303034076295</v>
+        <v>0.07869136757077196</v>
       </c>
       <c r="C8">
-        <v>525.0592527104296</v>
+        <v>520.1165201539858</v>
       </c>
       <c r="D8">
-        <v>523.1312527104296</v>
+        <v>523.7505201539858</v>
       </c>
       <c r="E8">
-        <v>-18.92800000000001</v>
+        <v>-13.36600000000001</v>
       </c>
       <c r="F8">
-        <v>33.37199999999999</v>
+        <v>38.93399999999999</v>
       </c>
       <c r="G8">
         <v>35.3</v>
@@ -2071,45 +2071,45 @@
         <v>23.2</v>
       </c>
       <c r="M8">
-        <v>1.6786116</v>
+        <v>2.0167812</v>
       </c>
       <c r="N8">
-        <v>21.5213884</v>
+        <v>21.1832188</v>
       </c>
       <c r="O8">
-        <v>4.30427768</v>
+        <v>4.23664376</v>
       </c>
       <c r="P8">
-        <v>17.21711072</v>
+        <v>16.94657504</v>
       </c>
       <c r="Q8">
-        <v>27.31711072</v>
+        <v>27.04657504</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08118713128471225</v>
+        <v>0.08149523394706662</v>
       </c>
       <c r="T8">
-        <v>0.6897610547718649</v>
+        <v>0.6957665491323356</v>
       </c>
       <c r="U8">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V8">
         <v>0.2</v>
       </c>
       <c r="W8">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y8">
-        <v>13.82094583404523</v>
+        <v>11.50347890985894</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2117,22 +2117,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07869136757077194</v>
+        <v>0.07858043173391442</v>
       </c>
       <c r="C9">
-        <v>520.116520153986</v>
+        <v>516.3270014540944</v>
       </c>
       <c r="D9">
-        <v>523.750520153986</v>
+        <v>525.5230014540945</v>
       </c>
       <c r="E9">
-        <v>-13.36600000000001</v>
+        <v>-7.804000000000009</v>
       </c>
       <c r="F9">
-        <v>38.934</v>
+        <v>44.496</v>
       </c>
       <c r="G9">
         <v>35.3</v>
@@ -2153,28 +2153,28 @@
         <v>23.2</v>
       </c>
       <c r="M9">
-        <v>2.0167812</v>
+        <v>2.3048928</v>
       </c>
       <c r="N9">
-        <v>21.1832188</v>
+        <v>20.8951072</v>
       </c>
       <c r="O9">
-        <v>4.23664376</v>
+        <v>4.17902144</v>
       </c>
       <c r="P9">
-        <v>16.94657504</v>
+        <v>16.71608576</v>
       </c>
       <c r="Q9">
-        <v>27.04657504</v>
+        <v>26.81608576</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08149523394706662</v>
+        <v>0.08181003449338523</v>
       </c>
       <c r="T9">
-        <v>0.6957665491323356</v>
+        <v>0.701902597718034</v>
       </c>
       <c r="U9">
         <v>0.0518</v>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>11.50347890985894</v>
+        <v>10.06554404612657</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2199,22 +2199,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07858043173391442</v>
+        <v>0.07859189589705685</v>
       </c>
       <c r="C10">
-        <v>516.3270014540944</v>
+        <v>510.5812767483719</v>
       </c>
       <c r="D10">
-        <v>525.5230014540945</v>
+        <v>525.339276748372</v>
       </c>
       <c r="E10">
-        <v>-7.804000000000009</v>
+        <v>-2.242000000000012</v>
       </c>
       <c r="F10">
-        <v>44.496</v>
+        <v>50.05799999999999</v>
       </c>
       <c r="G10">
         <v>35.3</v>
@@ -2235,45 +2235,45 @@
         <v>23.2</v>
       </c>
       <c r="M10">
-        <v>2.3048928</v>
+        <v>2.678103</v>
       </c>
       <c r="N10">
-        <v>20.8951072</v>
+        <v>20.521897</v>
       </c>
       <c r="O10">
-        <v>4.17902144</v>
+        <v>4.1043794</v>
       </c>
       <c r="P10">
-        <v>16.71608576</v>
+        <v>16.4175176</v>
       </c>
       <c r="Q10">
-        <v>26.81608576</v>
+        <v>26.5175176</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08181003449338523</v>
+        <v>0.08213175373302951</v>
       </c>
       <c r="T10">
-        <v>0.701902597718034</v>
+        <v>0.708173504514407</v>
       </c>
       <c r="U10">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V10">
         <v>0.2</v>
       </c>
       <c r="W10">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y10">
-        <v>10.06554404612657</v>
+        <v>8.662848292242682</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2281,22 +2281,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07859189589705685</v>
+        <v>0.07849456006019932</v>
       </c>
       <c r="C11">
-        <v>510.5812767483719</v>
+        <v>506.5832781615208</v>
       </c>
       <c r="D11">
-        <v>525.339276748372</v>
+        <v>526.9032781615208</v>
       </c>
       <c r="E11">
-        <v>-2.242000000000012</v>
+        <v>3.319999999999986</v>
       </c>
       <c r="F11">
-        <v>50.05799999999999</v>
+        <v>55.61999999999999</v>
       </c>
       <c r="G11">
         <v>35.3</v>
@@ -2317,28 +2317,28 @@
         <v>23.2</v>
       </c>
       <c r="M11">
-        <v>2.678103</v>
+        <v>2.97567</v>
       </c>
       <c r="N11">
-        <v>20.521897</v>
+        <v>20.22433</v>
       </c>
       <c r="O11">
-        <v>4.1043794</v>
+        <v>4.044866</v>
       </c>
       <c r="P11">
-        <v>16.4175176</v>
+        <v>16.179464</v>
       </c>
       <c r="Q11">
-        <v>26.5175176</v>
+        <v>26.279464</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08213175373302951</v>
+        <v>0.08246062228911034</v>
       </c>
       <c r="T11">
-        <v>0.708173504514407</v>
+        <v>0.7145837647951438</v>
       </c>
       <c r="U11">
         <v>0.0535</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>8.662848292242682</v>
+        <v>7.796563463018413</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2363,22 +2363,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07849456006019934</v>
+        <v>0.07846762422334176</v>
       </c>
       <c r="C12">
-        <v>506.5832781615205</v>
+        <v>501.455732183743</v>
       </c>
       <c r="D12">
-        <v>526.9032781615206</v>
+        <v>527.337732183743</v>
       </c>
       <c r="E12">
-        <v>3.319999999999993</v>
+        <v>8.881999999999991</v>
       </c>
       <c r="F12">
-        <v>55.62</v>
+        <v>61.182</v>
       </c>
       <c r="G12">
         <v>35.3</v>
@@ -2399,45 +2399,45 @@
         <v>23.2</v>
       </c>
       <c r="M12">
-        <v>2.97567</v>
+        <v>3.3221826</v>
       </c>
       <c r="N12">
-        <v>20.22433</v>
+        <v>19.8778174</v>
       </c>
       <c r="O12">
-        <v>4.044866</v>
+        <v>3.97556348</v>
       </c>
       <c r="P12">
-        <v>16.179464</v>
+        <v>15.90225392</v>
       </c>
       <c r="Q12">
-        <v>26.279464</v>
+        <v>26.00225391999999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08246062228911036</v>
+        <v>0.0827968811498222</v>
       </c>
       <c r="T12">
-        <v>0.714583764795144</v>
+        <v>0.7211380758687063</v>
       </c>
       <c r="U12">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V12">
         <v>0.2</v>
       </c>
       <c r="W12">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y12">
-        <v>7.796563463018413</v>
+        <v>6.983360878477902</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07846762422334176</v>
+        <v>0.07837668838648422</v>
       </c>
       <c r="C13">
-        <v>501.455732183743</v>
+        <v>497.3657632697075</v>
       </c>
       <c r="D13">
-        <v>527.337732183743</v>
+        <v>528.8097632697076</v>
       </c>
       <c r="E13">
-        <v>8.881999999999991</v>
+        <v>14.44399999999998</v>
       </c>
       <c r="F13">
-        <v>61.182</v>
+        <v>66.74399999999999</v>
       </c>
       <c r="G13">
         <v>35.3</v>
@@ -2481,28 +2481,28 @@
         <v>23.2</v>
       </c>
       <c r="M13">
-        <v>3.3221826</v>
+        <v>3.624199199999999</v>
       </c>
       <c r="N13">
-        <v>19.8778174</v>
+        <v>19.5758008</v>
       </c>
       <c r="O13">
-        <v>3.97556348</v>
+        <v>3.91516016</v>
       </c>
       <c r="P13">
-        <v>15.90225392</v>
+        <v>15.66064064</v>
       </c>
       <c r="Q13">
-        <v>26.00225391999999</v>
+        <v>25.76064064</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.0827968811498222</v>
+        <v>0.08314078225736843</v>
       </c>
       <c r="T13">
-        <v>0.7211380758687063</v>
+        <v>0.727841348557577</v>
       </c>
       <c r="U13">
         <v>0.0543</v>
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>6.983360878477902</v>
+        <v>6.401414138604745</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2527,22 +2527,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07837668838648422</v>
+        <v>0.07838975254962666</v>
       </c>
       <c r="C14">
-        <v>497.3657632697075</v>
+        <v>491.5917807758807</v>
       </c>
       <c r="D14">
-        <v>528.8097632697076</v>
+        <v>528.5977807758808</v>
       </c>
       <c r="E14">
-        <v>14.44399999999998</v>
+        <v>20.00599999999999</v>
       </c>
       <c r="F14">
-        <v>66.74399999999999</v>
+        <v>72.306</v>
       </c>
       <c r="G14">
         <v>35.3</v>
@@ -2563,45 +2563,45 @@
         <v>23.2</v>
       </c>
       <c r="M14">
-        <v>3.624199199999999</v>
+        <v>3.9985218</v>
       </c>
       <c r="N14">
-        <v>19.5758008</v>
+        <v>19.2014782</v>
       </c>
       <c r="O14">
-        <v>3.91516016</v>
+        <v>3.84029564</v>
       </c>
       <c r="P14">
-        <v>15.66064064</v>
+        <v>15.36118256</v>
       </c>
       <c r="Q14">
-        <v>25.76064064</v>
+        <v>25.46118256</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08314078225736843</v>
+        <v>0.0834925891375019</v>
       </c>
       <c r="T14">
-        <v>0.727841348557577</v>
+        <v>0.7346987194691802</v>
       </c>
       <c r="U14">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V14">
         <v>0.2</v>
       </c>
       <c r="W14">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y14">
-        <v>6.401414138604745</v>
+        <v>5.8021441823826</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2609,22 +2609,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07838975254962666</v>
+        <v>0.0783068167127691</v>
       </c>
       <c r="C15">
-        <v>491.5917807758807</v>
+        <v>487.3784117321835</v>
       </c>
       <c r="D15">
-        <v>528.5977807758808</v>
+        <v>529.9464117321835</v>
       </c>
       <c r="E15">
-        <v>20.00599999999999</v>
+        <v>25.56799999999999</v>
       </c>
       <c r="F15">
-        <v>72.306</v>
+        <v>77.86799999999999</v>
       </c>
       <c r="G15">
         <v>35.3</v>
@@ -2645,28 +2645,28 @@
         <v>23.2</v>
       </c>
       <c r="M15">
-        <v>3.9985218</v>
+        <v>4.3061004</v>
       </c>
       <c r="N15">
-        <v>19.2014782</v>
+        <v>18.8938996</v>
       </c>
       <c r="O15">
-        <v>3.84029564</v>
+        <v>3.77877992</v>
       </c>
       <c r="P15">
-        <v>15.36118256</v>
+        <v>15.11511968</v>
       </c>
       <c r="Q15">
-        <v>25.46118256</v>
+        <v>25.21511967999999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.0834925891375019</v>
+        <v>0.08385257757298734</v>
       </c>
       <c r="T15">
-        <v>0.7346987194691802</v>
+        <v>0.741715564122914</v>
       </c>
       <c r="U15">
         <v>0.0553</v>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>5.8021441823826</v>
+        <v>5.387705312212413</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2691,22 +2691,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.0783068167127691</v>
+        <v>0.07822388087591158</v>
       </c>
       <c r="C16">
-        <v>487.3784117321835</v>
+        <v>483.1719419142382</v>
       </c>
       <c r="D16">
-        <v>529.9464117321835</v>
+        <v>531.3019419142382</v>
       </c>
       <c r="E16">
-        <v>25.56799999999999</v>
+        <v>31.13</v>
       </c>
       <c r="F16">
-        <v>77.86799999999999</v>
+        <v>83.43000000000001</v>
       </c>
       <c r="G16">
         <v>35.3</v>
@@ -2727,28 +2727,28 @@
         <v>23.2</v>
       </c>
       <c r="M16">
-        <v>4.3061004</v>
+        <v>4.613679</v>
       </c>
       <c r="N16">
-        <v>18.8938996</v>
+        <v>18.586321</v>
       </c>
       <c r="O16">
-        <v>3.77877992</v>
+        <v>3.7172642</v>
       </c>
       <c r="P16">
-        <v>15.11511968</v>
+        <v>14.8690568</v>
       </c>
       <c r="Q16">
-        <v>25.21511967999999</v>
+        <v>24.9690568</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08385257757298734</v>
+        <v>0.08422103632460184</v>
       </c>
       <c r="T16">
-        <v>0.741715564122914</v>
+        <v>0.7488975110037942</v>
       </c>
       <c r="U16">
         <v>0.0553</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.387705312212413</v>
+        <v>5.028524958064919</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2773,22 +2773,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07822388087591158</v>
+        <v>0.078140945039054</v>
       </c>
       <c r="C17">
-        <v>483.1719419142382</v>
+        <v>478.9724243996295</v>
       </c>
       <c r="D17">
-        <v>531.3019419142382</v>
+        <v>532.6644243996295</v>
       </c>
       <c r="E17">
-        <v>31.12999999999999</v>
+        <v>36.69199999999999</v>
       </c>
       <c r="F17">
-        <v>83.42999999999999</v>
+        <v>88.99199999999999</v>
       </c>
       <c r="G17">
         <v>35.3</v>
@@ -2809,28 +2809,28 @@
         <v>23.2</v>
       </c>
       <c r="M17">
-        <v>4.613678999999999</v>
+        <v>4.9212576</v>
       </c>
       <c r="N17">
-        <v>18.586321</v>
+        <v>18.2787424</v>
       </c>
       <c r="O17">
-        <v>3.7172642</v>
+        <v>3.65574848</v>
       </c>
       <c r="P17">
-        <v>14.8690568</v>
+        <v>14.62299392</v>
       </c>
       <c r="Q17">
-        <v>24.9690568</v>
+        <v>24.72299392</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08422103632460184</v>
+        <v>0.08459826790363573</v>
       </c>
       <c r="T17">
-        <v>0.7488975110037942</v>
+        <v>0.7562504566199335</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.02852495806492</v>
+        <v>4.714242148185862</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2855,22 +2855,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.078140945039054</v>
+        <v>0.07839800920219646</v>
       </c>
       <c r="C18">
-        <v>478.9724243996295</v>
+        <v>469.2098938198411</v>
       </c>
       <c r="D18">
-        <v>532.6644243996295</v>
+        <v>528.4638938198411</v>
       </c>
       <c r="E18">
-        <v>36.69199999999999</v>
+        <v>42.254</v>
       </c>
       <c r="F18">
-        <v>88.99199999999999</v>
+        <v>94.554</v>
       </c>
       <c r="G18">
         <v>35.3</v>
@@ -2891,45 +2891,45 @@
         <v>23.2</v>
       </c>
       <c r="M18">
-        <v>4.9212576</v>
+        <v>5.4652212</v>
       </c>
       <c r="N18">
-        <v>18.2787424</v>
+        <v>17.7347788</v>
       </c>
       <c r="O18">
-        <v>3.65574848</v>
+        <v>3.54695576</v>
       </c>
       <c r="P18">
-        <v>14.62299392</v>
+        <v>14.18782304</v>
       </c>
       <c r="Q18">
-        <v>24.72299392</v>
+        <v>24.28782304</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08459826790363573</v>
+        <v>0.0849845894002367</v>
       </c>
       <c r="T18">
-        <v>0.7562504566199335</v>
+        <v>0.76378058164851</v>
       </c>
       <c r="U18">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V18">
         <v>0.2</v>
       </c>
       <c r="W18">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y18">
-        <v>4.714242148185862</v>
+        <v>4.245024885726492</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2937,22 +2937,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07839800920219646</v>
+        <v>0.07833507336533892</v>
       </c>
       <c r="C19">
-        <v>469.2098938198411</v>
+        <v>464.6701542288795</v>
       </c>
       <c r="D19">
-        <v>528.4638938198411</v>
+        <v>529.4861542288795</v>
       </c>
       <c r="E19">
-        <v>42.254</v>
+        <v>47.816</v>
       </c>
       <c r="F19">
-        <v>94.554</v>
+        <v>100.116</v>
       </c>
       <c r="G19">
         <v>35.3</v>
@@ -2973,28 +2973,28 @@
         <v>23.2</v>
       </c>
       <c r="M19">
-        <v>5.4652212</v>
+        <v>5.786704800000001</v>
       </c>
       <c r="N19">
-        <v>17.7347788</v>
+        <v>17.4132952</v>
       </c>
       <c r="O19">
-        <v>3.54695576</v>
+        <v>3.48265904</v>
       </c>
       <c r="P19">
-        <v>14.18782304</v>
+        <v>13.93063616</v>
       </c>
       <c r="Q19">
-        <v>24.28782304</v>
+        <v>24.03063616</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.0849845894002367</v>
+        <v>0.08538033337236453</v>
       </c>
       <c r="T19">
-        <v>0.76378058164851</v>
+        <v>0.7714943682631494</v>
       </c>
       <c r="U19">
         <v>0.0578</v>
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>4.245024885726492</v>
+        <v>4.009190169852797</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3019,22 +3019,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07833507336533892</v>
+        <v>0.07880413752848137</v>
       </c>
       <c r="C20">
-        <v>464.6701542288795</v>
+        <v>451.5829468328507</v>
       </c>
       <c r="D20">
-        <v>529.4861542288795</v>
+        <v>521.9609468328507</v>
       </c>
       <c r="E20">
-        <v>47.81599999999998</v>
+        <v>53.37799999999998</v>
       </c>
       <c r="F20">
-        <v>100.116</v>
+        <v>105.678</v>
       </c>
       <c r="G20">
         <v>35.3</v>
@@ -3055,45 +3055,45 @@
         <v>23.2</v>
       </c>
       <c r="M20">
-        <v>5.7867048</v>
+        <v>6.478061399999999</v>
       </c>
       <c r="N20">
-        <v>17.4132952</v>
+        <v>16.7219386</v>
       </c>
       <c r="O20">
-        <v>3.48265904</v>
+        <v>3.34438772</v>
       </c>
       <c r="P20">
-        <v>13.93063616</v>
+        <v>13.37755088</v>
       </c>
       <c r="Q20">
-        <v>24.03063616</v>
+        <v>23.47755088</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08538033337236453</v>
+        <v>0.08578584880059428</v>
       </c>
       <c r="T20">
-        <v>0.7714943682631493</v>
+        <v>0.7793986187448169</v>
       </c>
       <c r="U20">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V20">
         <v>0.2</v>
       </c>
       <c r="W20">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>4.009190169852798</v>
+        <v>3.581318324645704</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3101,22 +3101,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07880413752848137</v>
+        <v>0.07921720169162381</v>
       </c>
       <c r="C21">
-        <v>451.5829468328507</v>
+        <v>439.5690792083213</v>
       </c>
       <c r="D21">
-        <v>521.9609468328507</v>
+        <v>515.5090792083214</v>
       </c>
       <c r="E21">
-        <v>53.37799999999998</v>
+        <v>58.93999999999999</v>
       </c>
       <c r="F21">
-        <v>105.678</v>
+        <v>111.24</v>
       </c>
       <c r="G21">
         <v>35.3</v>
@@ -3137,45 +3137,45 @@
         <v>23.2</v>
       </c>
       <c r="M21">
-        <v>6.478061399999999</v>
+        <v>7.130484</v>
       </c>
       <c r="N21">
-        <v>16.7219386</v>
+        <v>16.069516</v>
       </c>
       <c r="O21">
-        <v>3.34438772</v>
+        <v>3.2139032</v>
       </c>
       <c r="P21">
-        <v>13.37755088</v>
+        <v>12.8556128</v>
       </c>
       <c r="Q21">
-        <v>23.47755088</v>
+        <v>22.9556128</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08578584880059428</v>
+        <v>0.08620150211452976</v>
       </c>
       <c r="T21">
-        <v>0.7793986187448169</v>
+        <v>0.7875004754885259</v>
       </c>
       <c r="U21">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V21">
         <v>0.2</v>
       </c>
       <c r="W21">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y21">
-        <v>3.581318324645704</v>
+        <v>3.253636078560726</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3183,22 +3183,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07921720169162381</v>
+        <v>0.07920466585476627</v>
       </c>
       <c r="C22">
-        <v>439.5690792083213</v>
+        <v>434.2005353483598</v>
       </c>
       <c r="D22">
-        <v>515.5090792083214</v>
+        <v>515.7025353483599</v>
       </c>
       <c r="E22">
-        <v>58.93999999999999</v>
+        <v>64.50199999999998</v>
       </c>
       <c r="F22">
-        <v>111.24</v>
+        <v>116.802</v>
       </c>
       <c r="G22">
         <v>35.3</v>
@@ -3219,28 +3219,28 @@
         <v>23.2</v>
       </c>
       <c r="M22">
-        <v>7.130484</v>
+        <v>7.4870082</v>
       </c>
       <c r="N22">
-        <v>16.069516</v>
+        <v>15.7129918</v>
       </c>
       <c r="O22">
-        <v>3.2139032</v>
+        <v>3.14259836</v>
       </c>
       <c r="P22">
-        <v>12.8556128</v>
+        <v>12.57039344</v>
       </c>
       <c r="Q22">
-        <v>22.9556128</v>
+        <v>22.67039344</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08620150211452976</v>
+        <v>0.08662767829717249</v>
       </c>
       <c r="T22">
-        <v>0.7875004754885259</v>
+        <v>0.7958074425295442</v>
       </c>
       <c r="U22">
         <v>0.0641</v>
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>3.253636078560726</v>
+        <v>3.098701027200691</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3265,22 +3265,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07920466585476627</v>
+        <v>0.08056493001790872</v>
       </c>
       <c r="C23">
-        <v>434.2005353483599</v>
+        <v>408.4603938329099</v>
       </c>
       <c r="D23">
-        <v>515.7025353483599</v>
+        <v>495.5243938329099</v>
       </c>
       <c r="E23">
-        <v>64.50199999999998</v>
+        <v>70.06399999999999</v>
       </c>
       <c r="F23">
-        <v>116.802</v>
+        <v>122.364</v>
       </c>
       <c r="G23">
         <v>35.3</v>
@@ -3301,45 +3301,45 @@
         <v>23.2</v>
       </c>
       <c r="M23">
-        <v>7.487008199999999</v>
+        <v>8.7979716</v>
       </c>
       <c r="N23">
-        <v>15.7129918</v>
+        <v>14.4020284</v>
       </c>
       <c r="O23">
-        <v>3.14259836</v>
+        <v>2.88040568</v>
       </c>
       <c r="P23">
-        <v>12.57039344</v>
+        <v>11.52162272</v>
       </c>
       <c r="Q23">
-        <v>22.67039344</v>
+        <v>21.62162272</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08662767829717249</v>
+        <v>0.08706478207424195</v>
       </c>
       <c r="T23">
-        <v>0.7958074425295442</v>
+        <v>0.8043274087254603</v>
       </c>
       <c r="U23">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V23">
         <v>0.2</v>
       </c>
       <c r="W23">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>3.098701027200692</v>
+        <v>2.636971458284771</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3347,22 +3347,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08056493001790872</v>
+        <v>0.08061479418105118</v>
       </c>
       <c r="C24">
-        <v>408.4603938329099</v>
+        <v>402.1886694241815</v>
       </c>
       <c r="D24">
-        <v>495.5243938329099</v>
+        <v>494.8146694241814</v>
       </c>
       <c r="E24">
-        <v>70.06399999999999</v>
+        <v>75.62599999999998</v>
       </c>
       <c r="F24">
-        <v>122.364</v>
+        <v>127.926</v>
       </c>
       <c r="G24">
         <v>35.3</v>
@@ -3383,28 +3383,28 @@
         <v>23.2</v>
       </c>
       <c r="M24">
-        <v>8.7979716</v>
+        <v>9.1978794</v>
       </c>
       <c r="N24">
-        <v>14.4020284</v>
+        <v>14.0021206</v>
       </c>
       <c r="O24">
-        <v>2.88040568</v>
+        <v>2.80042412</v>
       </c>
       <c r="P24">
-        <v>11.52162272</v>
+        <v>11.20169648</v>
       </c>
       <c r="Q24">
-        <v>21.62162272</v>
+        <v>21.30169648</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08706478207424195</v>
+        <v>0.08751323919617035</v>
       </c>
       <c r="T24">
-        <v>0.8043274087254603</v>
+        <v>0.8130686727446469</v>
       </c>
       <c r="U24">
         <v>0.07190000000000001</v>
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>2.636971458284771</v>
+        <v>2.522320525315868</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3429,22 +3429,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08061479418105118</v>
+        <v>0.08141345834419363</v>
       </c>
       <c r="C25">
-        <v>402.1886694241815</v>
+        <v>385.5300008544831</v>
       </c>
       <c r="D25">
-        <v>494.8146694241814</v>
+        <v>483.7180008544832</v>
       </c>
       <c r="E25">
-        <v>75.62599999999998</v>
+        <v>81.18799999999999</v>
       </c>
       <c r="F25">
-        <v>127.926</v>
+        <v>133.488</v>
       </c>
       <c r="G25">
         <v>35.3</v>
@@ -3465,45 +3465,45 @@
         <v>23.2</v>
       </c>
       <c r="M25">
-        <v>9.1978794</v>
+        <v>10.1183904</v>
       </c>
       <c r="N25">
-        <v>14.0021206</v>
+        <v>13.0816096</v>
       </c>
       <c r="O25">
-        <v>2.80042412</v>
+        <v>2.61632192</v>
       </c>
       <c r="P25">
-        <v>11.20169648</v>
+        <v>10.46528768</v>
       </c>
       <c r="Q25">
-        <v>21.30169648</v>
+        <v>20.56528768</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08751323919617035</v>
+        <v>0.08797349782130739</v>
       </c>
       <c r="T25">
-        <v>0.8130686727446469</v>
+        <v>0.8220399700274964</v>
       </c>
       <c r="U25">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V25">
         <v>0.2</v>
       </c>
       <c r="W25">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y25">
-        <v>2.522320525315868</v>
+        <v>2.292854800304997</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08141345834419363</v>
+        <v>0.08149452250733608</v>
       </c>
       <c r="C26">
-        <v>385.5300008544832</v>
+        <v>378.8694514922345</v>
       </c>
       <c r="D26">
-        <v>483.7180008544832</v>
+        <v>482.6194514922345</v>
       </c>
       <c r="E26">
-        <v>81.18799999999996</v>
+        <v>86.74999999999997</v>
       </c>
       <c r="F26">
-        <v>133.488</v>
+        <v>139.05</v>
       </c>
       <c r="G26">
         <v>35.3</v>
@@ -3547,28 +3547,28 @@
         <v>23.2</v>
       </c>
       <c r="M26">
-        <v>10.1183904</v>
+        <v>10.53999</v>
       </c>
       <c r="N26">
-        <v>13.0816096</v>
+        <v>12.66001</v>
       </c>
       <c r="O26">
-        <v>2.61632192</v>
+        <v>2.532002</v>
       </c>
       <c r="P26">
-        <v>10.46528768</v>
+        <v>10.128008</v>
       </c>
       <c r="Q26">
-        <v>20.56528768</v>
+        <v>20.228008</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08797349782130739</v>
+        <v>0.08844603000978142</v>
       </c>
       <c r="T26">
-        <v>0.8220399700274963</v>
+        <v>0.8312505019045551</v>
       </c>
       <c r="U26">
         <v>0.07580000000000001</v>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.292854800304998</v>
+        <v>2.201140608292797</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3593,22 +3593,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08149452250733608</v>
+        <v>0.08157558667047853</v>
       </c>
       <c r="C27">
-        <v>378.8694514922345</v>
+        <v>372.2138805520332</v>
       </c>
       <c r="D27">
-        <v>482.6194514922345</v>
+        <v>481.5258805520332</v>
       </c>
       <c r="E27">
-        <v>86.74999999999997</v>
+        <v>92.31199999999998</v>
       </c>
       <c r="F27">
-        <v>139.05</v>
+        <v>144.612</v>
       </c>
       <c r="G27">
         <v>35.3</v>
@@ -3629,28 +3629,28 @@
         <v>23.2</v>
       </c>
       <c r="M27">
-        <v>10.53999</v>
+        <v>10.9615896</v>
       </c>
       <c r="N27">
-        <v>12.66001</v>
+        <v>12.2384104</v>
       </c>
       <c r="O27">
-        <v>2.532002</v>
+        <v>2.44768208</v>
       </c>
       <c r="P27">
-        <v>10.128008</v>
+        <v>9.790728319999999</v>
       </c>
       <c r="Q27">
-        <v>20.228008</v>
+        <v>19.89072832</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08844603000978142</v>
+        <v>0.08893133333848449</v>
       </c>
       <c r="T27">
-        <v>0.8312505019045551</v>
+        <v>0.8407099670755884</v>
       </c>
       <c r="U27">
         <v>0.07580000000000001</v>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.201140608292797</v>
+        <v>2.11648135412769</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3675,22 +3675,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08157558667047853</v>
+        <v>0.08165665083362098</v>
       </c>
       <c r="C28">
-        <v>372.2138805520332</v>
+        <v>365.5632542684601</v>
       </c>
       <c r="D28">
-        <v>481.5258805520332</v>
+        <v>480.4372542684602</v>
       </c>
       <c r="E28">
-        <v>92.31199999999998</v>
+        <v>97.87399999999997</v>
       </c>
       <c r="F28">
-        <v>144.612</v>
+        <v>150.174</v>
       </c>
       <c r="G28">
         <v>35.3</v>
@@ -3711,28 +3711,28 @@
         <v>23.2</v>
       </c>
       <c r="M28">
-        <v>10.9615896</v>
+        <v>11.3831892</v>
       </c>
       <c r="N28">
-        <v>12.2384104</v>
+        <v>11.8168108</v>
       </c>
       <c r="O28">
-        <v>2.44768208</v>
+        <v>2.36336216</v>
       </c>
       <c r="P28">
-        <v>9.790728319999999</v>
+        <v>9.453448640000001</v>
       </c>
       <c r="Q28">
-        <v>19.89072832</v>
+        <v>19.55344864</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08893133333848449</v>
+        <v>0.08942993264879585</v>
       </c>
       <c r="T28">
-        <v>0.8407099670755884</v>
+        <v>0.8504285956759653</v>
       </c>
       <c r="U28">
         <v>0.07580000000000001</v>
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.11648135412769</v>
+        <v>2.038093155826664</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3757,22 +3757,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08165665083362098</v>
+        <v>0.08491851499676341</v>
       </c>
       <c r="C29">
-        <v>365.5632542684601</v>
+        <v>319.9404016909403</v>
       </c>
       <c r="D29">
-        <v>480.4372542684602</v>
+        <v>440.3764016909403</v>
       </c>
       <c r="E29">
-        <v>97.87399999999997</v>
+        <v>103.436</v>
       </c>
       <c r="F29">
-        <v>150.174</v>
+        <v>155.736</v>
       </c>
       <c r="G29">
         <v>35.3</v>
@@ -3793,45 +3793,45 @@
         <v>23.2</v>
       </c>
       <c r="M29">
-        <v>11.3831892</v>
+        <v>14.01624</v>
       </c>
       <c r="N29">
-        <v>11.8168108</v>
+        <v>9.183760000000001</v>
       </c>
       <c r="O29">
-        <v>2.36336216</v>
+        <v>1.836752</v>
       </c>
       <c r="P29">
-        <v>9.453448640000001</v>
+        <v>7.347008000000001</v>
       </c>
       <c r="Q29">
-        <v>19.55344864</v>
+        <v>17.447008</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08942993264879585</v>
+        <v>0.08994238193994919</v>
       </c>
       <c r="T29">
-        <v>0.8504285956759653</v>
+        <v>0.8604171861819079</v>
       </c>
       <c r="U29">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V29">
         <v>0.2</v>
       </c>
       <c r="W29">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y29">
-        <v>2.038093155826664</v>
+        <v>1.65522279869637</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3839,22 +3839,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08491851499676341</v>
+        <v>0.08511317915990586</v>
       </c>
       <c r="C30">
-        <v>319.9404016909403</v>
+        <v>312.1978224161336</v>
       </c>
       <c r="D30">
-        <v>440.3764016909403</v>
+        <v>438.1958224161336</v>
       </c>
       <c r="E30">
-        <v>103.436</v>
+        <v>108.998</v>
       </c>
       <c r="F30">
-        <v>155.736</v>
+        <v>161.298</v>
       </c>
       <c r="G30">
         <v>35.3</v>
@@ -3875,28 +3875,28 @@
         <v>23.2</v>
       </c>
       <c r="M30">
-        <v>14.01624</v>
+        <v>14.51682</v>
       </c>
       <c r="N30">
-        <v>9.183760000000001</v>
+        <v>8.68318</v>
       </c>
       <c r="O30">
-        <v>1.836752</v>
+        <v>1.736636</v>
       </c>
       <c r="P30">
-        <v>7.347008000000001</v>
+        <v>6.946544</v>
       </c>
       <c r="Q30">
-        <v>17.447008</v>
+        <v>17.046544</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08994238193994919</v>
+        <v>0.09046926642240263</v>
       </c>
       <c r="T30">
-        <v>0.8604171861819079</v>
+        <v>0.870687145434497</v>
       </c>
       <c r="U30">
         <v>0.09</v>
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>1.65522279869637</v>
+        <v>1.59814615046546</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3921,22 +3921,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08511317915990586</v>
+        <v>0.08530784332304832</v>
       </c>
       <c r="C31">
-        <v>312.1978224161336</v>
+        <v>304.4767315650926</v>
       </c>
       <c r="D31">
-        <v>438.1958224161336</v>
+        <v>436.0367315650926</v>
       </c>
       <c r="E31">
-        <v>108.998</v>
+        <v>114.56</v>
       </c>
       <c r="F31">
-        <v>161.298</v>
+        <v>166.86</v>
       </c>
       <c r="G31">
         <v>35.3</v>
@@ -3957,28 +3957,28 @@
         <v>23.2</v>
       </c>
       <c r="M31">
-        <v>14.51682</v>
+        <v>15.0174</v>
       </c>
       <c r="N31">
-        <v>8.683180000000002</v>
+        <v>8.182600000000001</v>
       </c>
       <c r="O31">
-        <v>1.736636000000001</v>
+        <v>1.63652</v>
       </c>
       <c r="P31">
-        <v>6.946544000000001</v>
+        <v>6.546080000000001</v>
       </c>
       <c r="Q31">
-        <v>17.046544</v>
+        <v>16.64608</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09046926642240263</v>
+        <v>0.09101120474721189</v>
       </c>
       <c r="T31">
-        <v>0.870687145434497</v>
+        <v>0.8812505320943028</v>
       </c>
       <c r="U31">
         <v>0.09</v>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>1.59814615046546</v>
+        <v>1.544874612116611</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4003,22 +4003,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08530784332304832</v>
+        <v>0.1005223213606305</v>
       </c>
       <c r="C32">
-        <v>304.4767315650926</v>
+        <v>177.6831918382521</v>
       </c>
       <c r="D32">
-        <v>436.0367315650926</v>
+        <v>314.8051918382521</v>
       </c>
       <c r="E32">
-        <v>114.56</v>
+        <v>120.122</v>
       </c>
       <c r="F32">
-        <v>166.86</v>
+        <v>172.422</v>
       </c>
       <c r="G32">
         <v>35.3</v>
@@ -4039,45 +4039,45 @@
         <v>23.2</v>
       </c>
       <c r="M32">
-        <v>15.0174</v>
+        <v>25.3115496</v>
       </c>
       <c r="N32">
-        <v>8.182600000000001</v>
+        <v>-2.1115496</v>
       </c>
       <c r="O32">
-        <v>1.63652</v>
+        <v>-0.42230992</v>
       </c>
       <c r="P32">
-        <v>6.546080000000001</v>
+        <v>-1.68923968</v>
       </c>
       <c r="Q32">
-        <v>16.64608</v>
+        <v>8.410760319999998</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09101120474721189</v>
+        <v>0.09182122357400026</v>
       </c>
       <c r="T32">
-        <v>0.8812505320943028</v>
+        <v>0.8970393067156577</v>
       </c>
       <c r="U32">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V32">
-        <v>0.2</v>
+        <v>0.1833155248622155</v>
       </c>
       <c r="W32">
-        <v>0.07199999999999999</v>
+        <v>0.1198892809502268</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y32">
-        <v>1.544874612116611</v>
+        <v>0.9165776243110774</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4085,22 +4085,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1005223213606305</v>
+        <v>0.1015323213606305</v>
       </c>
       <c r="C33">
-        <v>177.6831918382521</v>
+        <v>166.4161855511599</v>
       </c>
       <c r="D33">
-        <v>314.8051918382521</v>
+        <v>309.1001855511598</v>
       </c>
       <c r="E33">
-        <v>120.122</v>
+        <v>125.684</v>
       </c>
       <c r="F33">
-        <v>172.422</v>
+        <v>177.984</v>
       </c>
       <c r="G33">
         <v>35.3</v>
@@ -4121,37 +4121,37 @@
         <v>23.2</v>
       </c>
       <c r="M33">
-        <v>25.3115496</v>
+        <v>26.1280512</v>
       </c>
       <c r="N33">
-        <v>-2.1115496</v>
+        <v>-2.928051199999999</v>
       </c>
       <c r="O33">
-        <v>-0.42230992</v>
+        <v>-0.5856102399999997</v>
       </c>
       <c r="P33">
-        <v>-1.68923968</v>
+        <v>-2.342440959999999</v>
       </c>
       <c r="Q33">
-        <v>8.410760319999998</v>
+        <v>7.757559039999999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09182122357400026</v>
+        <v>0.09249800627361793</v>
       </c>
       <c r="T33">
-        <v>0.8970393067156577</v>
+        <v>0.9102310612261822</v>
       </c>
       <c r="U33">
         <v>0.1468</v>
       </c>
       <c r="V33">
-        <v>0.1833155248622155</v>
+        <v>0.1775869147102712</v>
       </c>
       <c r="W33">
-        <v>0.1198892809502268</v>
+        <v>0.1207302409205322</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.9165776243110774</v>
+        <v>0.8879345735513562</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4167,22 +4167,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1015323213606305</v>
+        <v>0.1025423213606305</v>
       </c>
       <c r="C34">
-        <v>166.4161855511599</v>
+        <v>155.352274809396</v>
       </c>
       <c r="D34">
-        <v>309.1001855511598</v>
+        <v>303.5982748093959</v>
       </c>
       <c r="E34">
-        <v>125.684</v>
+        <v>131.246</v>
       </c>
       <c r="F34">
-        <v>177.984</v>
+        <v>183.546</v>
       </c>
       <c r="G34">
         <v>35.3</v>
@@ -4203,37 +4203,37 @@
         <v>23.2</v>
       </c>
       <c r="M34">
-        <v>26.1280512</v>
+        <v>26.9445528</v>
       </c>
       <c r="N34">
-        <v>-2.928051199999999</v>
+        <v>-3.744552800000001</v>
       </c>
       <c r="O34">
-        <v>-0.5856102399999997</v>
+        <v>-0.7489105600000002</v>
       </c>
       <c r="P34">
-        <v>-2.342440959999999</v>
+        <v>-2.995642240000001</v>
       </c>
       <c r="Q34">
-        <v>7.757559039999999</v>
+        <v>7.104357759999997</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09249800627361793</v>
+        <v>0.09319499144188087</v>
       </c>
       <c r="T34">
-        <v>0.9102310612261822</v>
+        <v>0.9238165994534387</v>
       </c>
       <c r="U34">
         <v>0.1468</v>
       </c>
       <c r="V34">
-        <v>0.1775869147102712</v>
+        <v>0.1722054930523842</v>
       </c>
       <c r="W34">
-        <v>0.1207302409205322</v>
+        <v>0.12152023361991</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.8879345735513562</v>
+        <v>0.8610274652619211</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4249,22 +4249,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1025423213606305</v>
+        <v>0.1035523213606305</v>
       </c>
       <c r="C35">
-        <v>155.352274809396</v>
+        <v>144.4808041191577</v>
       </c>
       <c r="D35">
-        <v>303.5982748093959</v>
+        <v>298.2888041191576</v>
       </c>
       <c r="E35">
-        <v>131.246</v>
+        <v>136.808</v>
       </c>
       <c r="F35">
-        <v>183.546</v>
+        <v>189.108</v>
       </c>
       <c r="G35">
         <v>35.3</v>
@@ -4285,37 +4285,37 @@
         <v>23.2</v>
       </c>
       <c r="M35">
-        <v>26.9445528</v>
+        <v>27.7610544</v>
       </c>
       <c r="N35">
-        <v>-3.744552800000001</v>
+        <v>-4.561054400000003</v>
       </c>
       <c r="O35">
-        <v>-0.7489105600000002</v>
+        <v>-0.9122108800000007</v>
       </c>
       <c r="P35">
-        <v>-2.995642240000001</v>
+        <v>-3.648843520000002</v>
       </c>
       <c r="Q35">
-        <v>7.104357759999997</v>
+        <v>6.451156479999995</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09319499144188087</v>
+        <v>0.09391309737281847</v>
       </c>
       <c r="T35">
-        <v>0.9238165994534387</v>
+        <v>0.9378138206572787</v>
       </c>
       <c r="U35">
         <v>0.1468</v>
       </c>
       <c r="V35">
-        <v>0.1722054930523842</v>
+        <v>0.167140625609667</v>
       </c>
       <c r="W35">
-        <v>0.12152023361991</v>
+        <v>0.1222637561605009</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.8610274652619211</v>
+        <v>0.8357031280483351</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4331,22 +4331,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1035523213606305</v>
+        <v>0.1045623213606305</v>
       </c>
       <c r="C36">
-        <v>144.4808041191577</v>
+        <v>133.7918505682349</v>
       </c>
       <c r="D36">
-        <v>298.2888041191576</v>
+        <v>293.1618505682349</v>
       </c>
       <c r="E36">
-        <v>136.808</v>
+        <v>142.37</v>
       </c>
       <c r="F36">
-        <v>189.108</v>
+        <v>194.67</v>
       </c>
       <c r="G36">
         <v>35.3</v>
@@ -4367,37 +4367,37 @@
         <v>23.2</v>
       </c>
       <c r="M36">
-        <v>27.7610544</v>
+        <v>28.577556</v>
       </c>
       <c r="N36">
-        <v>-4.561054400000003</v>
+        <v>-5.377556000000002</v>
       </c>
       <c r="O36">
-        <v>-0.9122108800000007</v>
+        <v>-1.0755112</v>
       </c>
       <c r="P36">
-        <v>-3.648843520000002</v>
+        <v>-4.302044800000002</v>
       </c>
       <c r="Q36">
-        <v>6.451156479999995</v>
+        <v>5.797955199999996</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09391309737281847</v>
+        <v>0.09465329887086182</v>
       </c>
       <c r="T36">
-        <v>0.9378138206572787</v>
+        <v>0.9522417255904675</v>
       </c>
       <c r="U36">
         <v>0.1468</v>
       </c>
       <c r="V36">
-        <v>0.167140625609667</v>
+        <v>0.1623651791636765</v>
       </c>
       <c r="W36">
-        <v>0.1222637561605009</v>
+        <v>0.1229647916987723</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.8357031280483351</v>
+        <v>0.8118258958183827</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4413,22 +4413,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1045623213606305</v>
+        <v>0.1255268472808824</v>
       </c>
       <c r="C37">
-        <v>133.7918505682349</v>
+        <v>51.14164973402828</v>
       </c>
       <c r="D37">
-        <v>293.1618505682349</v>
+        <v>216.0736497340283</v>
       </c>
       <c r="E37">
-        <v>142.37</v>
+        <v>147.932</v>
       </c>
       <c r="F37">
-        <v>194.67</v>
+        <v>200.232</v>
       </c>
       <c r="G37">
         <v>35.3</v>
@@ -4449,45 +4449,45 @@
         <v>23.2</v>
       </c>
       <c r="M37">
-        <v>28.577556</v>
+        <v>40.2065856</v>
       </c>
       <c r="N37">
-        <v>-5.377556000000002</v>
+        <v>-17.0065856</v>
       </c>
       <c r="O37">
-        <v>-1.0755112</v>
+        <v>-3.401317120000001</v>
       </c>
       <c r="P37">
-        <v>-4.302044800000002</v>
+        <v>-13.60526848</v>
       </c>
       <c r="Q37">
-        <v>5.797955199999996</v>
+        <v>-3.505268480000005</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09465329887086182</v>
+        <v>0.0962205784161127</v>
       </c>
       <c r="T37">
-        <v>0.9522417255904675</v>
+        <v>0.9827909211032907</v>
       </c>
       <c r="U37">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V37">
-        <v>0.1623651791636765</v>
+        <v>0.1154039799887907</v>
       </c>
       <c r="W37">
-        <v>0.1229647916987723</v>
+        <v>0.1776268808182508</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y37">
-        <v>0.8118258958183827</v>
+        <v>0.5770198999439533</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4495,22 +4495,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1255268472808824</v>
+        <v>0.1270768472808824</v>
       </c>
       <c r="C38">
-        <v>51.14164973402831</v>
+        <v>41.4589909204509</v>
       </c>
       <c r="D38">
-        <v>216.0736497340283</v>
+        <v>211.9529909204509</v>
       </c>
       <c r="E38">
-        <v>147.932</v>
+        <v>153.494</v>
       </c>
       <c r="F38">
-        <v>200.232</v>
+        <v>205.794</v>
       </c>
       <c r="G38">
         <v>35.3</v>
@@ -4531,37 +4531,37 @@
         <v>23.2</v>
       </c>
       <c r="M38">
-        <v>40.2065856</v>
+        <v>41.3234352</v>
       </c>
       <c r="N38">
-        <v>-17.0065856</v>
+        <v>-18.1234352</v>
       </c>
       <c r="O38">
-        <v>-3.40131712</v>
+        <v>-3.62468704</v>
       </c>
       <c r="P38">
-        <v>-13.60526848</v>
+        <v>-14.49874816</v>
       </c>
       <c r="Q38">
-        <v>-3.50526848</v>
+        <v>-4.398748160000002</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09622057841611269</v>
+        <v>0.0970209050576383</v>
       </c>
       <c r="T38">
-        <v>0.9827909211032905</v>
+        <v>0.998390776993819</v>
       </c>
       <c r="U38">
         <v>0.2008</v>
       </c>
       <c r="V38">
-        <v>0.1154039799887907</v>
+        <v>0.1122849535026072</v>
       </c>
       <c r="W38">
-        <v>0.1776268808182508</v>
+        <v>0.1782531813366765</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.5770198999439535</v>
+        <v>0.5614247675130358</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1270768472808824</v>
+        <v>0.1286268472808824</v>
       </c>
       <c r="C39">
-        <v>41.4589909204509</v>
+        <v>31.93055797374475</v>
       </c>
       <c r="D39">
-        <v>211.9529909204509</v>
+        <v>207.9865579737447</v>
       </c>
       <c r="E39">
-        <v>153.494</v>
+        <v>159.056</v>
       </c>
       <c r="F39">
-        <v>205.794</v>
+        <v>211.356</v>
       </c>
       <c r="G39">
         <v>35.3</v>
@@ -4613,37 +4613,37 @@
         <v>23.2</v>
       </c>
       <c r="M39">
-        <v>41.3234352</v>
+        <v>42.44028479999999</v>
       </c>
       <c r="N39">
-        <v>-18.1234352</v>
+        <v>-19.24028479999999</v>
       </c>
       <c r="O39">
-        <v>-3.62468704</v>
+        <v>-3.848056959999999</v>
       </c>
       <c r="P39">
-        <v>-14.49874816</v>
+        <v>-15.39222783999999</v>
       </c>
       <c r="Q39">
-        <v>-4.398748160000002</v>
+        <v>-5.292227839999997</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.0970209050576383</v>
+        <v>0.09784704868760019</v>
       </c>
       <c r="T39">
-        <v>0.998390776993819</v>
+        <v>1.014493854042106</v>
       </c>
       <c r="U39">
         <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.1122849535026072</v>
+        <v>0.1093300863051701</v>
       </c>
       <c r="W39">
-        <v>0.1782531813366765</v>
+        <v>0.1788465186699219</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.5614247675130358</v>
+        <v>0.5466504315258507</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4659,22 +4659,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1286268472808824</v>
+        <v>0.1301768472808824</v>
       </c>
       <c r="C40">
-        <v>31.93055797374475</v>
+        <v>22.54785152110688</v>
       </c>
       <c r="D40">
-        <v>207.9865579737447</v>
+        <v>204.1658515211068</v>
       </c>
       <c r="E40">
-        <v>159.056</v>
+        <v>164.618</v>
       </c>
       <c r="F40">
-        <v>211.356</v>
+        <v>216.918</v>
       </c>
       <c r="G40">
         <v>35.3</v>
@@ -4695,37 +4695,37 @@
         <v>23.2</v>
       </c>
       <c r="M40">
-        <v>42.44028479999999</v>
+        <v>43.5571344</v>
       </c>
       <c r="N40">
-        <v>-19.24028479999999</v>
+        <v>-20.3571344</v>
       </c>
       <c r="O40">
-        <v>-3.848056959999999</v>
+        <v>-4.07142688</v>
       </c>
       <c r="P40">
-        <v>-15.39222783999999</v>
+        <v>-16.28570752</v>
       </c>
       <c r="Q40">
-        <v>-5.292227839999997</v>
+        <v>-6.185707519999998</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09784704868760019</v>
+        <v>0.09870027899395431</v>
       </c>
       <c r="T40">
-        <v>1.014493854042106</v>
+        <v>1.031124900829682</v>
       </c>
       <c r="U40">
         <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.1093300863051701</v>
+        <v>0.1065267507588837</v>
       </c>
       <c r="W40">
-        <v>0.1788465186699219</v>
+        <v>0.1794094284476161</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.5466504315258507</v>
+        <v>0.5326337537944186</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4741,22 +4741,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1301768472808824</v>
+        <v>0.1317268472808824</v>
       </c>
       <c r="C41">
-        <v>22.54785152110688</v>
+        <v>13.30298545686898</v>
       </c>
       <c r="D41">
-        <v>204.1658515211068</v>
+        <v>200.482985456869</v>
       </c>
       <c r="E41">
-        <v>164.618</v>
+        <v>170.18</v>
       </c>
       <c r="F41">
-        <v>216.918</v>
+        <v>222.48</v>
       </c>
       <c r="G41">
         <v>35.3</v>
@@ -4777,37 +4777,37 @@
         <v>23.2</v>
       </c>
       <c r="M41">
-        <v>43.5571344</v>
+        <v>44.673984</v>
       </c>
       <c r="N41">
-        <v>-20.3571344</v>
+        <v>-21.473984</v>
       </c>
       <c r="O41">
-        <v>-4.07142688</v>
+        <v>-4.294796799999999</v>
       </c>
       <c r="P41">
-        <v>-16.28570752</v>
+        <v>-17.1791872</v>
       </c>
       <c r="Q41">
-        <v>-6.185707519999998</v>
+        <v>-7.0791872</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09870027899395431</v>
+        <v>0.0995819503105202</v>
       </c>
       <c r="T41">
-        <v>1.031124900829682</v>
+        <v>1.04831031584351</v>
       </c>
       <c r="U41">
         <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.1065267507588837</v>
+        <v>0.1038635819899116</v>
       </c>
       <c r="W41">
-        <v>0.1794094284476161</v>
+        <v>0.1799441927364258</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.5326337537944186</v>
+        <v>0.5193179099495582</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4823,22 +4823,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1317268472808824</v>
+        <v>0.1332768472808824</v>
       </c>
       <c r="C42">
-        <v>13.30298545686898</v>
+        <v>4.188632610173926</v>
       </c>
       <c r="D42">
-        <v>200.482985456869</v>
+        <v>196.9306326101739</v>
       </c>
       <c r="E42">
-        <v>170.18</v>
+        <v>175.742</v>
       </c>
       <c r="F42">
-        <v>222.48</v>
+        <v>228.042</v>
       </c>
       <c r="G42">
         <v>35.3</v>
@@ -4859,37 +4859,37 @@
         <v>23.2</v>
       </c>
       <c r="M42">
-        <v>44.673984</v>
+        <v>45.7908336</v>
       </c>
       <c r="N42">
-        <v>-21.473984</v>
+        <v>-22.5908336</v>
       </c>
       <c r="O42">
-        <v>-4.294796799999999</v>
+        <v>-4.51816672</v>
       </c>
       <c r="P42">
-        <v>-17.1791872</v>
+        <v>-18.07266688</v>
       </c>
       <c r="Q42">
-        <v>-7.0791872</v>
+        <v>-7.972666880000002</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.0995819503105202</v>
+        <v>0.1004935087903595</v>
       </c>
       <c r="T42">
-        <v>1.04831031584351</v>
+        <v>1.066078287298485</v>
       </c>
       <c r="U42">
         <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.1038635819899116</v>
+        <v>0.1013303238925967</v>
       </c>
       <c r="W42">
-        <v>0.1799441927364258</v>
+        <v>0.1804528709623666</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.5193179099495582</v>
+        <v>0.5066516194629835</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4905,22 +4905,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1332768472808824</v>
+        <v>0.149734464704488</v>
       </c>
       <c r="C43">
-        <v>4.188632610173926</v>
+        <v>-32.55656556861953</v>
       </c>
       <c r="D43">
-        <v>196.9306326101739</v>
+        <v>165.7474344313805</v>
       </c>
       <c r="E43">
-        <v>175.742</v>
+        <v>181.304</v>
       </c>
       <c r="F43">
-        <v>228.042</v>
+        <v>233.604</v>
       </c>
       <c r="G43">
         <v>35.3</v>
@@ -4941,45 +4941,45 @@
         <v>23.2</v>
       </c>
       <c r="M43">
-        <v>45.7908336</v>
+        <v>55.0838232</v>
       </c>
       <c r="N43">
-        <v>-22.5908336</v>
+        <v>-31.8838232</v>
       </c>
       <c r="O43">
-        <v>-4.51816672</v>
+        <v>-6.37676464</v>
       </c>
       <c r="P43">
-        <v>-18.07266688</v>
+        <v>-25.50705856</v>
       </c>
       <c r="Q43">
-        <v>-7.972666880000002</v>
+        <v>-15.40705856</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1004935087903595</v>
+        <v>0.1017944613964098</v>
       </c>
       <c r="T43">
-        <v>1.066078287298485</v>
+        <v>1.091436275052217</v>
       </c>
       <c r="U43">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.1013303238925967</v>
+        <v>0.08423525693111295</v>
       </c>
       <c r="W43">
-        <v>0.1804528709623666</v>
+        <v>0.2159373264156436</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y43">
-        <v>0.5066516194629835</v>
+        <v>0.4211762846555648</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4987,22 +4987,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.149734464704488</v>
+        <v>0.151634464704488</v>
       </c>
       <c r="C44">
-        <v>-32.5565655686195</v>
+        <v>-41.09415699149812</v>
       </c>
       <c r="D44">
-        <v>165.7474344313805</v>
+        <v>162.7718430085019</v>
       </c>
       <c r="E44">
-        <v>181.3039999999999</v>
+        <v>186.866</v>
       </c>
       <c r="F44">
-        <v>233.604</v>
+        <v>239.166</v>
       </c>
       <c r="G44">
         <v>35.3</v>
@@ -5023,37 +5023,37 @@
         <v>23.2</v>
       </c>
       <c r="M44">
-        <v>55.08382319999999</v>
+        <v>56.39534279999999</v>
       </c>
       <c r="N44">
-        <v>-31.88382319999999</v>
+        <v>-33.19534279999999</v>
       </c>
       <c r="O44">
-        <v>-6.376764639999998</v>
+        <v>-6.639068559999998</v>
       </c>
       <c r="P44">
-        <v>-25.50705855999999</v>
+        <v>-26.55627423999999</v>
       </c>
       <c r="Q44">
-        <v>-15.40705856</v>
+        <v>-16.45627424</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1017944613964098</v>
+        <v>0.1027768203682767</v>
       </c>
       <c r="T44">
-        <v>1.091436275052217</v>
+        <v>1.110584279877694</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.08423525693111296</v>
+        <v>0.08227629746759869</v>
       </c>
       <c r="W44">
-        <v>0.2159373264156436</v>
+        <v>0.2163992490571403</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.4211762846555648</v>
+        <v>0.4113814873379935</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5069,22 +5069,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.151634464704488</v>
+        <v>0.153534464704488</v>
       </c>
       <c r="C45">
-        <v>-41.09415699149812</v>
+        <v>-49.52679363098449</v>
       </c>
       <c r="D45">
-        <v>162.7718430085019</v>
+        <v>159.9012063690155</v>
       </c>
       <c r="E45">
-        <v>186.866</v>
+        <v>192.428</v>
       </c>
       <c r="F45">
-        <v>239.166</v>
+        <v>244.728</v>
       </c>
       <c r="G45">
         <v>35.3</v>
@@ -5105,37 +5105,37 @@
         <v>23.2</v>
       </c>
       <c r="M45">
-        <v>56.39534279999999</v>
+        <v>57.7068624</v>
       </c>
       <c r="N45">
-        <v>-33.19534279999999</v>
+        <v>-34.5068624</v>
       </c>
       <c r="O45">
-        <v>-6.639068559999998</v>
+        <v>-6.901372480000001</v>
       </c>
       <c r="P45">
-        <v>-26.55627423999999</v>
+        <v>-27.60548992</v>
       </c>
       <c r="Q45">
-        <v>-16.45627424</v>
+        <v>-17.50548992000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1027768203682767</v>
+        <v>0.1037942635891387</v>
       </c>
       <c r="T45">
-        <v>1.110584279877694</v>
+        <v>1.130416142018368</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.08227629746759869</v>
+        <v>0.08040638161606235</v>
       </c>
       <c r="W45">
-        <v>0.2163992490571403</v>
+        <v>0.2168401752149325</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.4113814873379935</v>
+        <v>0.4020319080803118</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5151,22 +5151,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.153534464704488</v>
+        <v>0.155434464704488</v>
       </c>
       <c r="C46">
-        <v>-49.52679363098449</v>
+        <v>-57.85993218600038</v>
       </c>
       <c r="D46">
-        <v>159.9012063690155</v>
+        <v>157.1300678139996</v>
       </c>
       <c r="E46">
-        <v>192.428</v>
+        <v>197.99</v>
       </c>
       <c r="F46">
-        <v>244.728</v>
+        <v>250.29</v>
       </c>
       <c r="G46">
         <v>35.3</v>
@@ -5187,37 +5187,37 @@
         <v>23.2</v>
       </c>
       <c r="M46">
-        <v>57.7068624</v>
+        <v>59.018382</v>
       </c>
       <c r="N46">
-        <v>-34.5068624</v>
+        <v>-35.818382</v>
       </c>
       <c r="O46">
-        <v>-6.901372480000001</v>
+        <v>-7.1636764</v>
       </c>
       <c r="P46">
-        <v>-27.60548992</v>
+        <v>-28.6547056</v>
       </c>
       <c r="Q46">
-        <v>-17.50548992000001</v>
+        <v>-18.5547056</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1037942635891387</v>
+        <v>0.1048487047453049</v>
       </c>
       <c r="T46">
-        <v>1.130416142018368</v>
+        <v>1.150969162782338</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.08040638161606235</v>
+        <v>0.07861957313570543</v>
       </c>
       <c r="W46">
-        <v>0.2168401752149325</v>
+        <v>0.2172615046546007</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.4020319080803118</v>
+        <v>0.393097865678527</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5233,22 +5233,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.155434464704488</v>
+        <v>0.157334464704488</v>
       </c>
       <c r="C47">
-        <v>-57.85993218600038</v>
+        <v>-66.09865753396883</v>
       </c>
       <c r="D47">
-        <v>157.1300678139996</v>
+        <v>154.4533424660311</v>
       </c>
       <c r="E47">
-        <v>197.99</v>
+        <v>203.552</v>
       </c>
       <c r="F47">
-        <v>250.29</v>
+        <v>255.852</v>
       </c>
       <c r="G47">
         <v>35.3</v>
@@ -5269,37 +5269,37 @@
         <v>23.2</v>
       </c>
       <c r="M47">
-        <v>59.018382</v>
+        <v>60.3299016</v>
       </c>
       <c r="N47">
-        <v>-35.818382</v>
+        <v>-37.1299016</v>
       </c>
       <c r="O47">
-        <v>-7.1636764</v>
+        <v>-7.42598032</v>
       </c>
       <c r="P47">
-        <v>-28.6547056</v>
+        <v>-29.70392128</v>
       </c>
       <c r="Q47">
-        <v>-18.5547056</v>
+        <v>-19.60392128</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1048487047453049</v>
+        <v>0.1059421992776254</v>
       </c>
       <c r="T47">
-        <v>1.150969162782338</v>
+        <v>1.172283406537566</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.07861957313570543</v>
+        <v>0.07691045198058138</v>
       </c>
       <c r="W47">
-        <v>0.2172615046546007</v>
+        <v>0.2176645154229789</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.393097865678527</v>
+        <v>0.384552259902907</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5315,22 +5315,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.157334464704488</v>
+        <v>0.159234464704488</v>
       </c>
       <c r="C48">
-        <v>-66.09865753396883</v>
+        <v>-74.24771387041795</v>
       </c>
       <c r="D48">
-        <v>154.4533424660311</v>
+        <v>151.8662861295821</v>
       </c>
       <c r="E48">
-        <v>203.552</v>
+        <v>209.114</v>
       </c>
       <c r="F48">
-        <v>255.852</v>
+        <v>261.414</v>
       </c>
       <c r="G48">
         <v>35.3</v>
@@ -5351,37 +5351,37 @@
         <v>23.2</v>
       </c>
       <c r="M48">
-        <v>60.3299016</v>
+        <v>61.6414212</v>
       </c>
       <c r="N48">
-        <v>-37.1299016</v>
+        <v>-38.44142119999999</v>
       </c>
       <c r="O48">
-        <v>-7.42598032</v>
+        <v>-7.688284239999999</v>
       </c>
       <c r="P48">
-        <v>-29.70392128</v>
+        <v>-30.75313696</v>
       </c>
       <c r="Q48">
-        <v>-19.60392128</v>
+        <v>-20.65313696</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1059421992776254</v>
+        <v>0.1070769577545617</v>
       </c>
       <c r="T48">
-        <v>1.172283406537566</v>
+        <v>1.194401961377898</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.07691045198058138</v>
+        <v>0.07527405938524988</v>
       </c>
       <c r="W48">
-        <v>0.2176645154229789</v>
+        <v>0.2180503767969581</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.384552259902907</v>
+        <v>0.3763702969262493</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5397,22 +5397,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.159234464704488</v>
+        <v>0.161134464704488</v>
       </c>
       <c r="C49">
-        <v>-74.24771387041795</v>
+        <v>-82.31153277065323</v>
       </c>
       <c r="D49">
-        <v>151.8662861295821</v>
+        <v>149.3644672293468</v>
       </c>
       <c r="E49">
-        <v>209.114</v>
+        <v>214.676</v>
       </c>
       <c r="F49">
-        <v>261.414</v>
+        <v>266.976</v>
       </c>
       <c r="G49">
         <v>35.3</v>
@@ -5433,37 +5433,37 @@
         <v>23.2</v>
       </c>
       <c r="M49">
-        <v>61.6414212</v>
+        <v>62.9529408</v>
       </c>
       <c r="N49">
-        <v>-38.44142119999999</v>
+        <v>-39.7529408</v>
       </c>
       <c r="O49">
-        <v>-7.688284239999999</v>
+        <v>-7.950588160000001</v>
       </c>
       <c r="P49">
-        <v>-30.75313696</v>
+        <v>-31.80235264</v>
       </c>
       <c r="Q49">
-        <v>-20.65313696</v>
+        <v>-21.70235264</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1070769577545617</v>
+        <v>0.1082553607883033</v>
       </c>
       <c r="T49">
-        <v>1.194401961377898</v>
+        <v>1.217371229865934</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.07527405938524988</v>
+        <v>0.07370584981472382</v>
       </c>
       <c r="W49">
-        <v>0.2180503767969581</v>
+        <v>0.2184201606136881</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3763702969262493</v>
+        <v>0.3685292490736191</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5479,22 +5479,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.161134464704488</v>
+        <v>0.163034464704488</v>
       </c>
       <c r="C50">
-        <v>-82.31153277065317</v>
+        <v>-90.29425852268446</v>
       </c>
       <c r="D50">
-        <v>149.3644672293468</v>
+        <v>146.9437414773155</v>
       </c>
       <c r="E50">
-        <v>214.6759999999999</v>
+        <v>220.2379999999999</v>
       </c>
       <c r="F50">
-        <v>266.9759999999999</v>
+        <v>272.538</v>
       </c>
       <c r="G50">
         <v>35.3</v>
@@ -5515,37 +5515,37 @@
         <v>23.2</v>
       </c>
       <c r="M50">
-        <v>62.95294079999999</v>
+        <v>64.26446039999999</v>
       </c>
       <c r="N50">
-        <v>-39.75294079999999</v>
+        <v>-41.06446039999999</v>
       </c>
       <c r="O50">
-        <v>-7.950588159999999</v>
+        <v>-8.212892079999998</v>
       </c>
       <c r="P50">
-        <v>-31.80235263999999</v>
+        <v>-32.85156831999999</v>
       </c>
       <c r="Q50">
-        <v>-21.70235263999999</v>
+        <v>-22.75156831999999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1082553607883033</v>
+        <v>0.109479975705721</v>
       </c>
       <c r="T50">
-        <v>1.217371229865934</v>
+        <v>1.241241253980953</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.07370584981472385</v>
+        <v>0.07220164879809682</v>
       </c>
       <c r="W50">
-        <v>0.2184201606136881</v>
+        <v>0.2187748512134088</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3685292490736192</v>
+        <v>0.3610082439904841</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5561,22 +5561,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.163034464704488</v>
+        <v>0.164934464704488</v>
       </c>
       <c r="C51">
-        <v>-90.29425852268446</v>
+        <v>-98.19977103604015</v>
       </c>
       <c r="D51">
-        <v>146.9437414773155</v>
+        <v>144.6002289639598</v>
       </c>
       <c r="E51">
-        <v>220.2379999999999</v>
+        <v>225.8</v>
       </c>
       <c r="F51">
-        <v>272.538</v>
+        <v>278.1</v>
       </c>
       <c r="G51">
         <v>35.3</v>
@@ -5597,37 +5597,37 @@
         <v>23.2</v>
       </c>
       <c r="M51">
-        <v>64.26446039999999</v>
+        <v>65.57598</v>
       </c>
       <c r="N51">
-        <v>-41.06446039999999</v>
+        <v>-42.37598</v>
       </c>
       <c r="O51">
-        <v>-8.212892079999998</v>
+        <v>-8.475196</v>
       </c>
       <c r="P51">
-        <v>-32.85156831999999</v>
+        <v>-33.900784</v>
       </c>
       <c r="Q51">
-        <v>-22.75156831999999</v>
+        <v>-23.800784</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.109479975705721</v>
+        <v>0.1107535752198354</v>
       </c>
       <c r="T51">
-        <v>1.241241253980953</v>
+        <v>1.266066079060572</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.07220164879809682</v>
+        <v>0.07075761582213487</v>
       </c>
       <c r="W51">
-        <v>0.2187748512134088</v>
+        <v>0.2191153541891406</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3610082439904841</v>
+        <v>0.3537880791106744</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.164934464704488</v>
+        <v>0.166834464704488</v>
       </c>
       <c r="C52">
-        <v>-98.19977103604015</v>
+        <v>-106.0317065928447</v>
       </c>
       <c r="D52">
-        <v>144.6002289639598</v>
+        <v>142.3302934071552</v>
       </c>
       <c r="E52">
-        <v>225.8</v>
+        <v>231.362</v>
       </c>
       <c r="F52">
-        <v>278.1</v>
+        <v>283.662</v>
       </c>
       <c r="G52">
         <v>35.3</v>
@@ -5679,37 +5679,37 @@
         <v>23.2</v>
       </c>
       <c r="M52">
-        <v>65.57598</v>
+        <v>66.8874996</v>
       </c>
       <c r="N52">
-        <v>-42.37598</v>
+        <v>-43.6874996</v>
       </c>
       <c r="O52">
-        <v>-8.475196</v>
+        <v>-8.737499919999999</v>
       </c>
       <c r="P52">
-        <v>-33.900784</v>
+        <v>-34.94999968</v>
       </c>
       <c r="Q52">
-        <v>-23.800784</v>
+        <v>-24.84999968</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1107535752198354</v>
+        <v>0.1120791583875871</v>
       </c>
       <c r="T52">
-        <v>1.266066079060572</v>
+        <v>1.291904162306706</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.07075761582213487</v>
+        <v>0.06937021159032832</v>
       </c>
       <c r="W52">
-        <v>0.2191153541891406</v>
+        <v>0.2194425041070006</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3537880791106744</v>
+        <v>0.3468510579516416</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5725,22 +5725,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.166834464704488</v>
+        <v>0.168734464704488</v>
       </c>
       <c r="C53">
-        <v>-106.0317065928447</v>
+        <v>-113.7934766746005</v>
       </c>
       <c r="D53">
-        <v>142.3302934071552</v>
+        <v>140.1305233253995</v>
       </c>
       <c r="E53">
-        <v>231.362</v>
+        <v>236.924</v>
       </c>
       <c r="F53">
-        <v>283.662</v>
+        <v>289.224</v>
       </c>
       <c r="G53">
         <v>35.3</v>
@@ -5761,37 +5761,37 @@
         <v>23.2</v>
       </c>
       <c r="M53">
-        <v>66.8874996</v>
+        <v>68.1990192</v>
       </c>
       <c r="N53">
-        <v>-43.6874996</v>
+        <v>-44.99901919999999</v>
       </c>
       <c r="O53">
-        <v>-8.737499919999999</v>
+        <v>-8.999803839999998</v>
       </c>
       <c r="P53">
-        <v>-34.94999968</v>
+        <v>-35.99921535999999</v>
       </c>
       <c r="Q53">
-        <v>-24.84999968</v>
+        <v>-25.89921536</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1120791583875871</v>
+        <v>0.1134599741873285</v>
       </c>
       <c r="T53">
-        <v>1.291904162306706</v>
+        <v>1.318818832354762</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.06937021159032832</v>
+        <v>0.06803616905974508</v>
       </c>
       <c r="W53">
-        <v>0.2194425041070006</v>
+        <v>0.2197570713357121</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3468510579516416</v>
+        <v>0.3401808452987254</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5807,22 +5807,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.168734464704488</v>
+        <v>0.170634464704488</v>
       </c>
       <c r="C54">
-        <v>-113.7934766746005</v>
+        <v>-121.4882850696902</v>
       </c>
       <c r="D54">
-        <v>140.1305233253995</v>
+        <v>137.9977149303098</v>
       </c>
       <c r="E54">
-        <v>236.924</v>
+        <v>242.486</v>
       </c>
       <c r="F54">
-        <v>289.224</v>
+        <v>294.786</v>
       </c>
       <c r="G54">
         <v>35.3</v>
@@ -5843,37 +5843,37 @@
         <v>23.2</v>
       </c>
       <c r="M54">
-        <v>68.1990192</v>
+        <v>69.51053880000001</v>
       </c>
       <c r="N54">
-        <v>-44.99901919999999</v>
+        <v>-46.3105388</v>
       </c>
       <c r="O54">
-        <v>-8.999803839999998</v>
+        <v>-9.262107760000001</v>
       </c>
       <c r="P54">
-        <v>-35.99921535999999</v>
+        <v>-37.04843104</v>
       </c>
       <c r="Q54">
-        <v>-25.89921536</v>
+        <v>-26.94843104000001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1134599741873285</v>
+        <v>0.1148995481062079</v>
       </c>
       <c r="T54">
-        <v>1.318818832354762</v>
+        <v>1.346878807511247</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.06803616905974508</v>
+        <v>0.06675246775673101</v>
       </c>
       <c r="W54">
-        <v>0.2197570713357121</v>
+        <v>0.2200597681029628</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3401808452987254</v>
+        <v>0.333762338783655</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5889,22 +5889,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.170634464704488</v>
+        <v>0.172534464704488</v>
       </c>
       <c r="C55">
-        <v>-121.4882850696902</v>
+        <v>-129.1191434420277</v>
       </c>
       <c r="D55">
-        <v>137.9977149303098</v>
+        <v>135.9288565579723</v>
       </c>
       <c r="E55">
-        <v>242.486</v>
+        <v>248.0479999999999</v>
       </c>
       <c r="F55">
-        <v>294.786</v>
+        <v>300.348</v>
       </c>
       <c r="G55">
         <v>35.3</v>
@@ -5925,37 +5925,37 @@
         <v>23.2</v>
       </c>
       <c r="M55">
-        <v>69.51053880000001</v>
+        <v>70.82205839999999</v>
       </c>
       <c r="N55">
-        <v>-46.3105388</v>
+        <v>-47.62205839999999</v>
       </c>
       <c r="O55">
-        <v>-9.262107760000001</v>
+        <v>-9.524411679999998</v>
       </c>
       <c r="P55">
-        <v>-37.04843104</v>
+        <v>-38.09764671999999</v>
       </c>
       <c r="Q55">
-        <v>-26.94843104000001</v>
+        <v>-27.99764671999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1148995481062079</v>
+        <v>0.1164017121954732</v>
       </c>
       <c r="T55">
-        <v>1.346878807511247</v>
+        <v>1.376158781587578</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.06675246775673101</v>
+        <v>0.06551631094642119</v>
       </c>
       <c r="W55">
-        <v>0.2200597681029628</v>
+        <v>0.2203512538788339</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.333762338783655</v>
+        <v>0.327581554732106</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5971,22 +5971,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.172534464704488</v>
+        <v>0.174434464704488</v>
       </c>
       <c r="C56">
-        <v>-129.1191434420277</v>
+        <v>-136.688885519965</v>
       </c>
       <c r="D56">
-        <v>135.9288565579723</v>
+        <v>133.9211144800349</v>
       </c>
       <c r="E56">
-        <v>248.0479999999999</v>
+        <v>253.61</v>
       </c>
       <c r="F56">
-        <v>300.348</v>
+        <v>305.91</v>
       </c>
       <c r="G56">
         <v>35.3</v>
@@ -6007,37 +6007,37 @@
         <v>23.2</v>
       </c>
       <c r="M56">
-        <v>70.82205839999999</v>
+        <v>72.133578</v>
       </c>
       <c r="N56">
-        <v>-47.62205839999999</v>
+        <v>-48.933578</v>
       </c>
       <c r="O56">
-        <v>-9.524411679999998</v>
+        <v>-9.786715600000001</v>
       </c>
       <c r="P56">
-        <v>-38.09764671999999</v>
+        <v>-39.1468624</v>
       </c>
       <c r="Q56">
-        <v>-27.99764671999999</v>
+        <v>-29.0468624</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1164017121954732</v>
+        <v>0.1179706391331505</v>
       </c>
       <c r="T56">
-        <v>1.376158781587578</v>
+        <v>1.40674008784508</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.06551631094642119</v>
+        <v>0.06432510529284989</v>
       </c>
       <c r="W56">
-        <v>0.2203512538788339</v>
+        <v>0.220632140171946</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.327581554732106</v>
+        <v>0.3216255264642495</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6053,22 +6053,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.174434464704488</v>
+        <v>0.176334464704488</v>
       </c>
       <c r="C57">
-        <v>-136.688885519965</v>
+        <v>-144.2001800460361</v>
       </c>
       <c r="D57">
-        <v>133.9211144800349</v>
+        <v>131.9718199539639</v>
       </c>
       <c r="E57">
-        <v>253.61</v>
+        <v>259.172</v>
       </c>
       <c r="F57">
-        <v>305.91</v>
+        <v>311.472</v>
       </c>
       <c r="G57">
         <v>35.3</v>
@@ -6089,37 +6089,37 @@
         <v>23.2</v>
       </c>
       <c r="M57">
-        <v>72.133578</v>
+        <v>73.4450976</v>
       </c>
       <c r="N57">
-        <v>-48.933578</v>
+        <v>-50.24509759999999</v>
       </c>
       <c r="O57">
-        <v>-9.786715600000001</v>
+        <v>-10.04901952</v>
       </c>
       <c r="P57">
-        <v>-39.1468624</v>
+        <v>-40.19607807999999</v>
       </c>
       <c r="Q57">
-        <v>-29.0468624</v>
+        <v>-30.09607807999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1179706391331505</v>
+        <v>0.1196108809316311</v>
       </c>
       <c r="T57">
-        <v>1.40674008784508</v>
+        <v>1.438711453477923</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.06432510529284989</v>
+        <v>0.06317644269833471</v>
       </c>
       <c r="W57">
-        <v>0.220632140171946</v>
+        <v>0.2209029948117327</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3216255264642495</v>
+        <v>0.3158822134916736</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6135,22 +6135,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.176334464704488</v>
+        <v>0.178234464704488</v>
       </c>
       <c r="C58">
-        <v>-144.2001800460361</v>
+        <v>-151.6555426119817</v>
       </c>
       <c r="D58">
-        <v>131.9718199539639</v>
+        <v>130.0784573880183</v>
       </c>
       <c r="E58">
-        <v>259.172</v>
+        <v>264.734</v>
       </c>
       <c r="F58">
-        <v>311.472</v>
+        <v>317.034</v>
       </c>
       <c r="G58">
         <v>35.3</v>
@@ -6171,37 +6171,37 @@
         <v>23.2</v>
       </c>
       <c r="M58">
-        <v>73.4450976</v>
+        <v>74.75661720000001</v>
       </c>
       <c r="N58">
-        <v>-50.24509759999999</v>
+        <v>-51.55661720000001</v>
       </c>
       <c r="O58">
-        <v>-10.04901952</v>
+        <v>-10.31132344</v>
       </c>
       <c r="P58">
-        <v>-40.19607807999999</v>
+        <v>-41.24529376</v>
       </c>
       <c r="Q58">
-        <v>-30.09607807999999</v>
+        <v>-31.14529376</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1196108809316311</v>
+        <v>0.1213274130463202</v>
       </c>
       <c r="T58">
-        <v>1.438711453477923</v>
+        <v>1.472169859372758</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.06317644269833471</v>
+        <v>0.06206808405450427</v>
       </c>
       <c r="W58">
-        <v>0.2209029948117327</v>
+        <v>0.2211643457799479</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3158822134916736</v>
+        <v>0.3103404202725214</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6217,22 +6217,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.178234464704488</v>
+        <v>0.180134464704488</v>
       </c>
       <c r="C59">
-        <v>-151.6555426119817</v>
+        <v>-159.0573464894225</v>
       </c>
       <c r="D59">
-        <v>130.0784573880183</v>
+        <v>128.2386535105776</v>
       </c>
       <c r="E59">
-        <v>264.734</v>
+        <v>270.296</v>
       </c>
       <c r="F59">
-        <v>317.034</v>
+        <v>322.596</v>
       </c>
       <c r="G59">
         <v>35.3</v>
@@ -6253,37 +6253,37 @@
         <v>23.2</v>
       </c>
       <c r="M59">
-        <v>74.75661720000001</v>
+        <v>76.0681368</v>
       </c>
       <c r="N59">
-        <v>-51.55661720000001</v>
+        <v>-52.8681368</v>
       </c>
       <c r="O59">
-        <v>-10.31132344</v>
+        <v>-10.57362736</v>
       </c>
       <c r="P59">
-        <v>-41.24529376</v>
+        <v>-42.29450944</v>
       </c>
       <c r="Q59">
-        <v>-31.14529376</v>
+        <v>-32.19450944</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1213274130463202</v>
+        <v>0.1231256847855183</v>
       </c>
       <c r="T59">
-        <v>1.472169859372758</v>
+        <v>1.507221522691157</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.06206808405450427</v>
+        <v>0.06099794467425419</v>
       </c>
       <c r="W59">
-        <v>0.2211643457799479</v>
+        <v>0.2214166846458109</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3103404202725214</v>
+        <v>0.3049897233712711</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6299,22 +6299,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.180134464704488</v>
+        <v>0.182034464704488</v>
       </c>
       <c r="C60">
-        <v>-159.0573464894224</v>
+        <v>-166.407832554227</v>
       </c>
       <c r="D60">
-        <v>128.2386535105776</v>
+        <v>126.4501674457729</v>
       </c>
       <c r="E60">
-        <v>270.2959999999999</v>
+        <v>275.8579999999999</v>
       </c>
       <c r="F60">
-        <v>322.5959999999999</v>
+        <v>328.158</v>
       </c>
       <c r="G60">
         <v>35.3</v>
@@ -6335,37 +6335,37 @@
         <v>23.2</v>
       </c>
       <c r="M60">
-        <v>76.06813679999999</v>
+        <v>77.37965639999999</v>
       </c>
       <c r="N60">
-        <v>-52.86813679999999</v>
+        <v>-54.17965639999998</v>
       </c>
       <c r="O60">
-        <v>-10.57362736</v>
+        <v>-10.83593128</v>
       </c>
       <c r="P60">
-        <v>-42.29450943999999</v>
+        <v>-43.34372511999999</v>
       </c>
       <c r="Q60">
-        <v>-32.19450943999999</v>
+        <v>-33.24372511999999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1231256847855183</v>
+        <v>0.1250116770973602</v>
       </c>
       <c r="T60">
-        <v>1.507221522691157</v>
+        <v>1.5439830232446</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.06099794467425421</v>
+        <v>0.05996408120519905</v>
       </c>
       <c r="W60">
-        <v>0.2214166846458109</v>
+        <v>0.2216604696518141</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3049897233712711</v>
+        <v>0.2998204060259954</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6381,22 +6381,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.182034464704488</v>
+        <v>0.183934464704488</v>
       </c>
       <c r="C61">
-        <v>-166.407832554227</v>
+        <v>-173.7091183918415</v>
       </c>
       <c r="D61">
-        <v>126.4501674457729</v>
+        <v>124.7108816081585</v>
       </c>
       <c r="E61">
-        <v>275.8579999999999</v>
+        <v>281.42</v>
       </c>
       <c r="F61">
-        <v>328.158</v>
+        <v>333.72</v>
       </c>
       <c r="G61">
         <v>35.3</v>
@@ -6417,37 +6417,37 @@
         <v>23.2</v>
       </c>
       <c r="M61">
-        <v>77.37965639999999</v>
+        <v>78.691176</v>
       </c>
       <c r="N61">
-        <v>-54.17965639999998</v>
+        <v>-55.491176</v>
       </c>
       <c r="O61">
-        <v>-10.83593128</v>
+        <v>-11.0982352</v>
       </c>
       <c r="P61">
-        <v>-43.34372511999999</v>
+        <v>-44.3929408</v>
       </c>
       <c r="Q61">
-        <v>-33.24372511999999</v>
+        <v>-34.2929408</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1250116770973602</v>
+        <v>0.1269919690247942</v>
       </c>
       <c r="T61">
-        <v>1.5439830232446</v>
+        <v>1.582582598825715</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.05996408120519905</v>
+        <v>0.05896467985177906</v>
       </c>
       <c r="W61">
-        <v>0.2216604696518141</v>
+        <v>0.2218961284909505</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2998204060259954</v>
+        <v>0.2948233992588953</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6463,22 +6463,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.183934464704488</v>
+        <v>0.185834464704488</v>
       </c>
       <c r="C62">
-        <v>-173.7091183918415</v>
+        <v>-180.9632066613652</v>
       </c>
       <c r="D62">
-        <v>124.7108816081585</v>
+        <v>123.0187933386348</v>
       </c>
       <c r="E62">
-        <v>281.42</v>
+        <v>286.9819999999999</v>
       </c>
       <c r="F62">
-        <v>333.72</v>
+        <v>339.2819999999999</v>
       </c>
       <c r="G62">
         <v>35.3</v>
@@ -6499,37 +6499,37 @@
         <v>23.2</v>
       </c>
       <c r="M62">
-        <v>78.691176</v>
+        <v>80.00269559999998</v>
       </c>
       <c r="N62">
-        <v>-55.491176</v>
+        <v>-56.80269559999998</v>
       </c>
       <c r="O62">
-        <v>-11.0982352</v>
+        <v>-11.36053912</v>
       </c>
       <c r="P62">
-        <v>-44.3929408</v>
+        <v>-45.44215647999998</v>
       </c>
       <c r="Q62">
-        <v>-34.2929408</v>
+        <v>-35.34215647999999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1269919690247942</v>
+        <v>0.1290738143844043</v>
       </c>
       <c r="T62">
-        <v>1.582582598825715</v>
+        <v>1.623161639821246</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.05896467985177906</v>
+        <v>0.05799804575584827</v>
       </c>
       <c r="W62">
-        <v>0.2218961284909505</v>
+        <v>0.222124060810771</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2948233992588953</v>
+        <v>0.2899902287792414</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6545,22 +6545,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.185834464704488</v>
+        <v>0.187734464704488</v>
       </c>
       <c r="C63">
-        <v>-180.9632066613652</v>
+        <v>-188.171992787836</v>
       </c>
       <c r="D63">
-        <v>123.0187933386348</v>
+        <v>121.3720072121639</v>
       </c>
       <c r="E63">
-        <v>286.9819999999999</v>
+        <v>292.5439999999999</v>
       </c>
       <c r="F63">
-        <v>339.2819999999999</v>
+        <v>344.8439999999999</v>
       </c>
       <c r="G63">
         <v>35.3</v>
@@ -6581,37 +6581,37 @@
         <v>23.2</v>
       </c>
       <c r="M63">
-        <v>80.00269559999998</v>
+        <v>81.31421519999999</v>
       </c>
       <c r="N63">
-        <v>-56.80269559999998</v>
+        <v>-58.11421519999999</v>
       </c>
       <c r="O63">
-        <v>-11.36053912</v>
+        <v>-11.62284304</v>
       </c>
       <c r="P63">
-        <v>-45.44215647999998</v>
+        <v>-46.49137215999999</v>
       </c>
       <c r="Q63">
-        <v>-35.34215647999999</v>
+        <v>-36.39137215999999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1290738143844043</v>
+        <v>0.131265230552415</v>
       </c>
       <c r="T63">
-        <v>1.623161639821246</v>
+        <v>1.665876419816542</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.05799804575584827</v>
+        <v>0.05706259340494749</v>
       </c>
       <c r="W63">
-        <v>0.222124060810771</v>
+        <v>0.2223446404751134</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2899902287792414</v>
+        <v>0.2853129670247374</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6627,22 +6627,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.187734464704488</v>
+        <v>0.189634464704488</v>
       </c>
       <c r="C64">
-        <v>-188.171992787836</v>
+        <v>-195.3372720448409</v>
       </c>
       <c r="D64">
-        <v>121.3720072121639</v>
+        <v>119.7687279551591</v>
       </c>
       <c r="E64">
-        <v>292.5439999999999</v>
+        <v>298.1059999999999</v>
       </c>
       <c r="F64">
-        <v>344.8439999999999</v>
+        <v>350.4059999999999</v>
       </c>
       <c r="G64">
         <v>35.3</v>
@@ -6663,37 +6663,37 @@
         <v>23.2</v>
       </c>
       <c r="M64">
-        <v>81.31421519999999</v>
+        <v>82.62573479999999</v>
       </c>
       <c r="N64">
-        <v>-58.11421519999999</v>
+        <v>-59.42573479999999</v>
       </c>
       <c r="O64">
-        <v>-11.62284304</v>
+        <v>-11.88514696</v>
       </c>
       <c r="P64">
-        <v>-46.49137215999999</v>
+        <v>-47.54058783999999</v>
       </c>
       <c r="Q64">
-        <v>-36.39137215999999</v>
+        <v>-37.44058783999999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.131265230552415</v>
+        <v>0.1335751016484262</v>
       </c>
       <c r="T64">
-        <v>1.665876419816542</v>
+        <v>1.71090010683861</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.05706259340494749</v>
+        <v>0.05615683795407531</v>
       </c>
       <c r="W64">
-        <v>0.2223446404751134</v>
+        <v>0.222558217610429</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2853129670247374</v>
+        <v>0.2807841897703766</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.189634464704488</v>
+        <v>0.191534464704488</v>
       </c>
       <c r="C65">
-        <v>-195.3372720448409</v>
+        <v>-202.4607460830943</v>
       </c>
       <c r="D65">
-        <v>119.7687279551591</v>
+        <v>118.2072539169057</v>
       </c>
       <c r="E65">
-        <v>298.1059999999999</v>
+        <v>303.6679999999999</v>
       </c>
       <c r="F65">
-        <v>350.4059999999999</v>
+        <v>355.968</v>
       </c>
       <c r="G65">
         <v>35.3</v>
@@ -6745,37 +6745,37 @@
         <v>23.2</v>
       </c>
       <c r="M65">
-        <v>82.62573479999999</v>
+        <v>83.9372544</v>
       </c>
       <c r="N65">
-        <v>-59.42573479999999</v>
+        <v>-60.7372544</v>
       </c>
       <c r="O65">
-        <v>-11.88514696</v>
+        <v>-12.14745088</v>
       </c>
       <c r="P65">
-        <v>-47.54058783999999</v>
+        <v>-48.58980352</v>
       </c>
       <c r="Q65">
-        <v>-37.44058783999999</v>
+        <v>-38.48980352</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1335751016484262</v>
+        <v>0.136013298916438</v>
       </c>
       <c r="T65">
-        <v>1.71090010683861</v>
+        <v>1.75842510980635</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.05615683795407531</v>
+        <v>0.05527938736104287</v>
       </c>
       <c r="W65">
-        <v>0.222558217610429</v>
+        <v>0.2227651204602661</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2807841897703766</v>
+        <v>0.2763969368052144</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6791,22 +6791,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.191534464704488</v>
+        <v>0.193434464704488</v>
       </c>
       <c r="C66">
-        <v>-202.4607460830943</v>
+        <v>-209.5440289548931</v>
       </c>
       <c r="D66">
-        <v>118.2072539169057</v>
+        <v>116.6859710451069</v>
       </c>
       <c r="E66">
-        <v>303.6679999999999</v>
+        <v>309.23</v>
       </c>
       <c r="F66">
-        <v>355.968</v>
+        <v>361.53</v>
       </c>
       <c r="G66">
         <v>35.3</v>
@@ -6827,37 +6827,37 @@
         <v>23.2</v>
       </c>
       <c r="M66">
-        <v>83.9372544</v>
+        <v>85.248774</v>
       </c>
       <c r="N66">
-        <v>-60.7372544</v>
+        <v>-62.04877399999999</v>
       </c>
       <c r="O66">
-        <v>-12.14745088</v>
+        <v>-12.4097548</v>
       </c>
       <c r="P66">
-        <v>-48.58980352</v>
+        <v>-49.63901919999999</v>
       </c>
       <c r="Q66">
-        <v>-38.48980352</v>
+        <v>-39.5390192</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.136013298916438</v>
+        <v>0.138590821742622</v>
       </c>
       <c r="T66">
-        <v>1.75842510980635</v>
+        <v>1.808665827229388</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.05527938736104287</v>
+        <v>0.05442893524779605</v>
       </c>
       <c r="W66">
-        <v>0.2227651204602661</v>
+        <v>0.2229656570685697</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2763969368052144</v>
+        <v>0.2721446762389803</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6873,22 +6873,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.193434464704488</v>
+        <v>0.195334464704488</v>
       </c>
       <c r="C67">
-        <v>-209.5440289548931</v>
+        <v>-216.5886526792889</v>
       </c>
       <c r="D67">
-        <v>116.6859710451069</v>
+        <v>115.2033473207111</v>
       </c>
       <c r="E67">
-        <v>309.23</v>
+        <v>314.792</v>
       </c>
       <c r="F67">
-        <v>361.53</v>
+        <v>367.092</v>
       </c>
       <c r="G67">
         <v>35.3</v>
@@ -6909,37 +6909,37 @@
         <v>23.2</v>
       </c>
       <c r="M67">
-        <v>85.248774</v>
+        <v>86.56029359999999</v>
       </c>
       <c r="N67">
-        <v>-62.04877399999999</v>
+        <v>-63.36029359999999</v>
       </c>
       <c r="O67">
-        <v>-12.4097548</v>
+        <v>-12.67205872</v>
       </c>
       <c r="P67">
-        <v>-49.63901919999999</v>
+        <v>-50.68823488</v>
       </c>
       <c r="Q67">
-        <v>-39.5390192</v>
+        <v>-40.58823488</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.138590821742622</v>
+        <v>0.1413199635585815</v>
       </c>
       <c r="T67">
-        <v>1.808665827229388</v>
+        <v>1.861861880971429</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.05442893524779605</v>
+        <v>0.05360425441070824</v>
       </c>
       <c r="W67">
-        <v>0.2229656570685697</v>
+        <v>0.223160116809955</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2721446762389803</v>
+        <v>0.2680212720535412</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6955,22 +6955,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.195334464704488</v>
+        <v>0.197234464704488</v>
       </c>
       <c r="C68">
-        <v>-216.5886526792889</v>
+        <v>-223.5960723883128</v>
       </c>
       <c r="D68">
-        <v>115.2033473207111</v>
+        <v>113.7579276116872</v>
       </c>
       <c r="E68">
-        <v>314.792</v>
+        <v>320.354</v>
       </c>
       <c r="F68">
-        <v>367.092</v>
+        <v>372.654</v>
       </c>
       <c r="G68">
         <v>35.3</v>
@@ -6991,37 +6991,37 @@
         <v>23.2</v>
       </c>
       <c r="M68">
-        <v>86.56029359999999</v>
+        <v>87.87181320000001</v>
       </c>
       <c r="N68">
-        <v>-63.36029359999999</v>
+        <v>-64.6718132</v>
       </c>
       <c r="O68">
-        <v>-12.67205872</v>
+        <v>-12.93436264</v>
       </c>
       <c r="P68">
-        <v>-50.68823488</v>
+        <v>-51.73745056</v>
       </c>
       <c r="Q68">
-        <v>-40.58823488</v>
+        <v>-41.63745056</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1413199635585815</v>
+        <v>0.1442145079088415</v>
       </c>
       <c r="T68">
-        <v>1.861861880971429</v>
+        <v>1.918281937970564</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.05360425441070824</v>
+        <v>0.05280419091204095</v>
       </c>
       <c r="W68">
-        <v>0.223160116809955</v>
+        <v>0.2233487717829408</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2680212720535412</v>
+        <v>0.2640209545602048</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7037,22 +7037,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.197234464704488</v>
+        <v>0.199134464704488</v>
       </c>
       <c r="C69">
-        <v>-223.5960723883128</v>
+        <v>-230.5676710905926</v>
       </c>
       <c r="D69">
-        <v>113.7579276116872</v>
+        <v>112.3483289094074</v>
       </c>
       <c r="E69">
-        <v>320.354</v>
+        <v>325.916</v>
       </c>
       <c r="F69">
-        <v>372.654</v>
+        <v>378.216</v>
       </c>
       <c r="G69">
         <v>35.3</v>
@@ -7073,37 +7073,37 @@
         <v>23.2</v>
       </c>
       <c r="M69">
-        <v>87.87181320000001</v>
+        <v>89.1833328</v>
       </c>
       <c r="N69">
-        <v>-64.6718132</v>
+        <v>-65.9833328</v>
       </c>
       <c r="O69">
-        <v>-12.93436264</v>
+        <v>-13.19666656</v>
       </c>
       <c r="P69">
-        <v>-51.73745056</v>
+        <v>-52.78666624</v>
       </c>
       <c r="Q69">
-        <v>-41.63745056</v>
+        <v>-42.68666624000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1442145079088415</v>
+        <v>0.1472899612809928</v>
       </c>
       <c r="T69">
-        <v>1.918281937970564</v>
+        <v>1.978228248532144</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.05280419091204095</v>
+        <v>0.05202765869274623</v>
       </c>
       <c r="W69">
-        <v>0.2233487717829408</v>
+        <v>0.2235318780802505</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2640209545602048</v>
+        <v>0.2601382934637312</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7119,22 +7119,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.199134464704488</v>
+        <v>0.201034464704488</v>
       </c>
       <c r="C70">
-        <v>-230.5676710905926</v>
+        <v>-237.5047640851426</v>
       </c>
       <c r="D70">
-        <v>112.3483289094074</v>
+        <v>110.9732359148574</v>
       </c>
       <c r="E70">
-        <v>325.916</v>
+        <v>331.478</v>
       </c>
       <c r="F70">
-        <v>378.216</v>
+        <v>383.778</v>
       </c>
       <c r="G70">
         <v>35.3</v>
@@ -7155,37 +7155,37 @@
         <v>23.2</v>
       </c>
       <c r="M70">
-        <v>89.1833328</v>
+        <v>90.4948524</v>
       </c>
       <c r="N70">
-        <v>-65.9833328</v>
+        <v>-67.2948524</v>
       </c>
       <c r="O70">
-        <v>-13.19666656</v>
+        <v>-13.45897048</v>
       </c>
       <c r="P70">
-        <v>-52.78666624</v>
+        <v>-53.83588192</v>
       </c>
       <c r="Q70">
-        <v>-42.68666624000001</v>
+        <v>-43.73588192</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1472899612809928</v>
+        <v>0.1505638309997345</v>
       </c>
       <c r="T70">
-        <v>1.978228248532144</v>
+        <v>2.042042063000923</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.05202765869274623</v>
+        <v>0.05127363465372092</v>
       </c>
       <c r="W70">
-        <v>0.2235318780802505</v>
+        <v>0.2237096769486526</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2601382934637312</v>
+        <v>0.2563681732686046</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7201,22 +7201,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.201034464704488</v>
+        <v>0.202934464704488</v>
       </c>
       <c r="C71">
-        <v>-237.5047640851426</v>
+        <v>-244.4086030549367</v>
       </c>
       <c r="D71">
-        <v>110.9732359148574</v>
+        <v>109.6313969450632</v>
       </c>
       <c r="E71">
-        <v>331.478</v>
+        <v>337.04</v>
       </c>
       <c r="F71">
-        <v>383.778</v>
+        <v>389.34</v>
       </c>
       <c r="G71">
         <v>35.3</v>
@@ -7237,37 +7237,37 @@
         <v>23.2</v>
       </c>
       <c r="M71">
-        <v>90.4948524</v>
+        <v>91.806372</v>
       </c>
       <c r="N71">
-        <v>-67.2948524</v>
+        <v>-68.60637199999999</v>
       </c>
       <c r="O71">
-        <v>-13.45897048</v>
+        <v>-13.7212744</v>
       </c>
       <c r="P71">
-        <v>-53.83588192</v>
+        <v>-54.88509759999999</v>
       </c>
       <c r="Q71">
-        <v>-43.73588192</v>
+        <v>-44.7850976</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1505638309997345</v>
+        <v>0.1540559586997257</v>
       </c>
       <c r="T71">
-        <v>2.042042063000923</v>
+        <v>2.11011013176762</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.05127363465372092</v>
+        <v>0.05054115415866777</v>
       </c>
       <c r="W71">
-        <v>0.2237096769486526</v>
+        <v>0.2238823958493862</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2563681732686046</v>
+        <v>0.2527057707933389</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7283,22 +7283,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.202934464704488</v>
+        <v>0.204834464704488</v>
       </c>
       <c r="C72">
-        <v>-244.4086030549367</v>
+        <v>-251.2803798670428</v>
       </c>
       <c r="D72">
-        <v>109.6313969450632</v>
+        <v>108.3216201329572</v>
       </c>
       <c r="E72">
-        <v>337.04</v>
+        <v>342.602</v>
       </c>
       <c r="F72">
-        <v>389.34</v>
+        <v>394.902</v>
       </c>
       <c r="G72">
         <v>35.3</v>
@@ -7319,37 +7319,37 @@
         <v>23.2</v>
       </c>
       <c r="M72">
-        <v>91.806372</v>
+        <v>93.11789160000001</v>
       </c>
       <c r="N72">
-        <v>-68.60637199999999</v>
+        <v>-69.9178916</v>
       </c>
       <c r="O72">
-        <v>-13.7212744</v>
+        <v>-13.98357832</v>
       </c>
       <c r="P72">
-        <v>-54.88509759999999</v>
+        <v>-55.93431328</v>
       </c>
       <c r="Q72">
-        <v>-44.7850976</v>
+        <v>-45.83431328</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1540559586997257</v>
+        <v>0.1577889227928197</v>
       </c>
       <c r="T72">
-        <v>2.11011013176762</v>
+        <v>2.182872550104435</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.05054115415866777</v>
+        <v>0.04982930691699639</v>
       </c>
       <c r="W72">
-        <v>0.2238823958493862</v>
+        <v>0.2240502494289723</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2527057707933389</v>
+        <v>0.2491465345849819</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7365,22 +7365,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.204834464704488</v>
+        <v>0.206734464704488</v>
       </c>
       <c r="C73">
-        <v>-251.2803798670427</v>
+        <v>-258.1212301035693</v>
       </c>
       <c r="D73">
-        <v>108.3216201329573</v>
+        <v>107.0427698964306</v>
       </c>
       <c r="E73">
-        <v>342.6019999999999</v>
+        <v>348.1639999999999</v>
       </c>
       <c r="F73">
-        <v>394.9019999999999</v>
+        <v>400.4639999999999</v>
       </c>
       <c r="G73">
         <v>35.3</v>
@@ -7401,37 +7401,37 @@
         <v>23.2</v>
       </c>
       <c r="M73">
-        <v>93.11789159999999</v>
+        <v>94.42941119999999</v>
       </c>
       <c r="N73">
-        <v>-69.91789159999999</v>
+        <v>-71.22941119999999</v>
       </c>
       <c r="O73">
-        <v>-13.98357832</v>
+        <v>-14.24588224</v>
       </c>
       <c r="P73">
-        <v>-55.93431327999999</v>
+        <v>-56.98352895999999</v>
       </c>
       <c r="Q73">
-        <v>-45.83431327999999</v>
+        <v>-46.88352895999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1577889227928196</v>
+        <v>0.1617885271782775</v>
       </c>
       <c r="T73">
-        <v>2.182872550104434</v>
+        <v>2.260832284036735</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.04982930691699639</v>
+        <v>0.04913723320981589</v>
       </c>
       <c r="W73">
-        <v>0.2240502494289723</v>
+        <v>0.2242134404091254</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.249146534584982</v>
+        <v>0.2456861660490794</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7447,22 +7447,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.206734464704488</v>
+        <v>0.208634464704488</v>
       </c>
       <c r="C74">
-        <v>-258.1212301035693</v>
+        <v>-264.9322363454132</v>
       </c>
       <c r="D74">
-        <v>107.0427698964306</v>
+        <v>105.7937636545867</v>
       </c>
       <c r="E74">
-        <v>348.1639999999999</v>
+        <v>353.7259999999999</v>
       </c>
       <c r="F74">
-        <v>400.4639999999999</v>
+        <v>406.026</v>
       </c>
       <c r="G74">
         <v>35.3</v>
@@ -7483,37 +7483,37 @@
         <v>23.2</v>
       </c>
       <c r="M74">
-        <v>94.42941119999999</v>
+        <v>95.74093079999999</v>
       </c>
       <c r="N74">
-        <v>-71.22941119999999</v>
+        <v>-72.54093079999998</v>
       </c>
       <c r="O74">
-        <v>-14.24588224</v>
+        <v>-14.50818616</v>
       </c>
       <c r="P74">
-        <v>-56.98352895999999</v>
+        <v>-58.03274463999999</v>
       </c>
       <c r="Q74">
-        <v>-46.88352895999999</v>
+        <v>-47.93274464</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1617885271782775</v>
+        <v>0.1660843985552507</v>
       </c>
       <c r="T74">
-        <v>2.260832284036735</v>
+        <v>2.344566813075132</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.04913723320981589</v>
+        <v>0.04846412042611978</v>
       </c>
       <c r="W74">
-        <v>0.2242134404091254</v>
+        <v>0.224372160403521</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2456861660490794</v>
+        <v>0.2423206021305989</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7529,22 +7529,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.208634464704488</v>
+        <v>0.210534464704488</v>
       </c>
       <c r="C75">
-        <v>-264.9322363454132</v>
+        <v>-271.7144312287626</v>
       </c>
       <c r="D75">
-        <v>105.7937636545867</v>
+        <v>104.5735687712374</v>
       </c>
       <c r="E75">
-        <v>353.7259999999999</v>
+        <v>359.288</v>
       </c>
       <c r="F75">
-        <v>406.026</v>
+        <v>411.588</v>
       </c>
       <c r="G75">
         <v>35.3</v>
@@ -7565,37 +7565,37 @@
         <v>23.2</v>
       </c>
       <c r="M75">
-        <v>95.74093079999999</v>
+        <v>97.0524504</v>
       </c>
       <c r="N75">
-        <v>-72.54093079999998</v>
+        <v>-73.8524504</v>
       </c>
       <c r="O75">
-        <v>-14.50818616</v>
+        <v>-14.77049008</v>
       </c>
       <c r="P75">
-        <v>-58.03274463999999</v>
+        <v>-59.08196031999999</v>
       </c>
       <c r="Q75">
-        <v>-47.93274464</v>
+        <v>-48.98196032</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1660843985552507</v>
+        <v>0.1707107215766065</v>
       </c>
       <c r="T75">
-        <v>2.344566813075132</v>
+        <v>2.434742459731869</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.04846412042611978</v>
+        <v>0.04780919987982086</v>
       </c>
       <c r="W75">
-        <v>0.224372160403521</v>
+        <v>0.2245265906683382</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2423206021305989</v>
+        <v>0.2390459993991043</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7611,22 +7611,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.210534464704488</v>
+        <v>0.212434464704488</v>
       </c>
       <c r="C76">
-        <v>-271.7144312287626</v>
+        <v>-278.4688002924957</v>
       </c>
       <c r="D76">
-        <v>104.5735687712374</v>
+        <v>103.3811997075043</v>
       </c>
       <c r="E76">
-        <v>359.288</v>
+        <v>364.85</v>
       </c>
       <c r="F76">
-        <v>411.588</v>
+        <v>417.15</v>
       </c>
       <c r="G76">
         <v>35.3</v>
@@ -7647,37 +7647,37 @@
         <v>23.2</v>
       </c>
       <c r="M76">
-        <v>97.0524504</v>
+        <v>98.36396999999999</v>
       </c>
       <c r="N76">
-        <v>-73.8524504</v>
+        <v>-75.16396999999999</v>
       </c>
       <c r="O76">
-        <v>-14.77049008</v>
+        <v>-15.032794</v>
       </c>
       <c r="P76">
-        <v>-59.08196031999999</v>
+        <v>-60.131176</v>
       </c>
       <c r="Q76">
-        <v>-48.98196032</v>
+        <v>-50.031176</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1707107215766065</v>
+        <v>0.1757071504396708</v>
       </c>
       <c r="T76">
-        <v>2.434742459731869</v>
+        <v>2.532132158121144</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.04780919987982086</v>
+        <v>0.04717174388142326</v>
       </c>
       <c r="W76">
-        <v>0.2245265906683382</v>
+        <v>0.2246769027927604</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2390459993991043</v>
+        <v>0.2358587194071163</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7693,22 +7693,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.212434464704488</v>
+        <v>0.214334464704488</v>
       </c>
       <c r="C77">
-        <v>-278.4688002924957</v>
+        <v>-285.1962846329757</v>
       </c>
       <c r="D77">
-        <v>103.3811997075043</v>
+        <v>102.2157153670243</v>
       </c>
       <c r="E77">
-        <v>364.85</v>
+        <v>370.4119999999999</v>
       </c>
       <c r="F77">
-        <v>417.15</v>
+        <v>422.7119999999999</v>
       </c>
       <c r="G77">
         <v>35.3</v>
@@ -7729,37 +7729,37 @@
         <v>23.2</v>
       </c>
       <c r="M77">
-        <v>98.36396999999999</v>
+        <v>99.67548959999999</v>
       </c>
       <c r="N77">
-        <v>-75.16396999999999</v>
+        <v>-76.47548959999999</v>
       </c>
       <c r="O77">
-        <v>-15.032794</v>
+        <v>-15.29509792</v>
       </c>
       <c r="P77">
-        <v>-60.131176</v>
+        <v>-61.18039167999999</v>
       </c>
       <c r="Q77">
-        <v>-50.031176</v>
+        <v>-51.08039167999999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1757071504396708</v>
+        <v>0.1811199483746571</v>
       </c>
       <c r="T77">
-        <v>2.532132158121144</v>
+        <v>2.637637664709525</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.04717174388142326</v>
+        <v>0.04655106304087821</v>
       </c>
       <c r="W77">
-        <v>0.2246769027927604</v>
+        <v>0.2248232593349609</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2358587194071163</v>
+        <v>0.2327553152043911</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7775,22 +7775,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.214334464704488</v>
+        <v>0.216234464704488</v>
       </c>
       <c r="C78">
-        <v>-285.1962846329757</v>
+        <v>-291.8977833812721</v>
       </c>
       <c r="D78">
-        <v>102.2157153670243</v>
+        <v>101.0762166187278</v>
       </c>
       <c r="E78">
-        <v>370.4119999999999</v>
+        <v>375.9739999999999</v>
       </c>
       <c r="F78">
-        <v>422.7119999999999</v>
+        <v>428.2739999999999</v>
       </c>
       <c r="G78">
         <v>35.3</v>
@@ -7811,37 +7811,37 @@
         <v>23.2</v>
       </c>
       <c r="M78">
-        <v>99.67548959999999</v>
+        <v>100.9870092</v>
       </c>
       <c r="N78">
-        <v>-76.47548959999999</v>
+        <v>-77.78700919999999</v>
       </c>
       <c r="O78">
-        <v>-15.29509792</v>
+        <v>-15.55740184</v>
       </c>
       <c r="P78">
-        <v>-61.18039167999999</v>
+        <v>-62.22960735999999</v>
       </c>
       <c r="Q78">
-        <v>-51.08039167999999</v>
+        <v>-52.12960735999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1811199483746571</v>
+        <v>0.1870034243909465</v>
       </c>
       <c r="T78">
-        <v>2.637637664709525</v>
+        <v>2.752317563175156</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.04655106304087821</v>
+        <v>0.04594650378060706</v>
       </c>
       <c r="W78">
-        <v>0.2248232593349609</v>
+        <v>0.2249658144085329</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2327553152043911</v>
+        <v>0.2297325189030354</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7857,22 +7857,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.216234464704488</v>
+        <v>0.218134464704488</v>
       </c>
       <c r="C79">
-        <v>-291.8977833812721</v>
+        <v>-298.5741560165131</v>
       </c>
       <c r="D79">
-        <v>101.0762166187278</v>
+        <v>99.96184398348684</v>
       </c>
       <c r="E79">
-        <v>375.9739999999999</v>
+        <v>381.5359999999999</v>
       </c>
       <c r="F79">
-        <v>428.2739999999999</v>
+        <v>433.836</v>
       </c>
       <c r="G79">
         <v>35.3</v>
@@ -7893,37 +7893,37 @@
         <v>23.2</v>
       </c>
       <c r="M79">
-        <v>100.9870092</v>
+        <v>102.2985288</v>
       </c>
       <c r="N79">
-        <v>-77.78700919999999</v>
+        <v>-79.0985288</v>
       </c>
       <c r="O79">
-        <v>-15.55740184</v>
+        <v>-15.81970576</v>
       </c>
       <c r="P79">
-        <v>-62.22960735999999</v>
+        <v>-63.27882304</v>
       </c>
       <c r="Q79">
-        <v>-52.12960735999999</v>
+        <v>-53.17882304</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1870034243909465</v>
+        <v>0.1934217618632623</v>
       </c>
       <c r="T79">
-        <v>2.752317563175156</v>
+        <v>2.877422906955845</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.04594650378060706</v>
+        <v>0.04535744603983005</v>
       </c>
       <c r="W79">
-        <v>0.2249658144085329</v>
+        <v>0.2251047142238081</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2297325189030354</v>
+        <v>0.2267872301991503</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7939,22 +7939,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.218134464704488</v>
+        <v>0.220034464704488</v>
       </c>
       <c r="C80">
-        <v>-298.5741560165131</v>
+        <v>-305.2262245278765</v>
       </c>
       <c r="D80">
-        <v>99.96184398348684</v>
+        <v>98.87177547212343</v>
       </c>
       <c r="E80">
-        <v>381.5359999999999</v>
+        <v>387.098</v>
       </c>
       <c r="F80">
-        <v>433.836</v>
+        <v>439.398</v>
       </c>
       <c r="G80">
         <v>35.3</v>
@@ -7975,37 +7975,37 @@
         <v>23.2</v>
       </c>
       <c r="M80">
-        <v>102.2985288</v>
+        <v>103.6100484</v>
       </c>
       <c r="N80">
-        <v>-79.0985288</v>
+        <v>-80.41004839999999</v>
       </c>
       <c r="O80">
-        <v>-15.81970576</v>
+        <v>-16.08200968</v>
       </c>
       <c r="P80">
-        <v>-63.27882304</v>
+        <v>-64.32803872</v>
       </c>
       <c r="Q80">
-        <v>-53.17882304</v>
+        <v>-54.22803872</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1934217618632623</v>
+        <v>0.2004513695710367</v>
       </c>
       <c r="T80">
-        <v>2.877422906955845</v>
+        <v>3.014443045382314</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.04535744603983005</v>
+        <v>0.04478330115324992</v>
       </c>
       <c r="W80">
-        <v>0.2251047142238081</v>
+        <v>0.2252400975880637</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2267872301991503</v>
+        <v>0.2239165057662497</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8021,22 +8021,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.220034464704488</v>
+        <v>0.221934464704488</v>
       </c>
       <c r="C81">
-        <v>-305.2262245278765</v>
+        <v>-311.8547754366508</v>
       </c>
       <c r="D81">
-        <v>98.87177547212343</v>
+        <v>97.80522456334916</v>
       </c>
       <c r="E81">
-        <v>387.098</v>
+        <v>392.66</v>
       </c>
       <c r="F81">
-        <v>439.398</v>
+        <v>444.96</v>
       </c>
       <c r="G81">
         <v>35.3</v>
@@ -8057,37 +8057,37 @@
         <v>23.2</v>
       </c>
       <c r="M81">
-        <v>103.6100484</v>
+        <v>104.921568</v>
       </c>
       <c r="N81">
-        <v>-80.41004839999999</v>
+        <v>-81.72156799999999</v>
       </c>
       <c r="O81">
-        <v>-16.08200968</v>
+        <v>-16.3443136</v>
       </c>
       <c r="P81">
-        <v>-64.32803872</v>
+        <v>-65.3772544</v>
       </c>
       <c r="Q81">
-        <v>-54.22803872</v>
+        <v>-55.2772544</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2004513695710367</v>
+        <v>0.2081839380495885</v>
       </c>
       <c r="T81">
-        <v>3.014443045382314</v>
+        <v>3.16516519765143</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.04478330115324992</v>
+        <v>0.0442235098888343</v>
       </c>
       <c r="W81">
-        <v>0.2252400975880637</v>
+        <v>0.2253720963682129</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2239165057662497</v>
+        <v>0.2211175494441715</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8103,22 +8103,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.221934464704488</v>
+        <v>0.223834464704488</v>
       </c>
       <c r="C82">
-        <v>-311.8547754366508</v>
+        <v>-318.4605616888173</v>
       </c>
       <c r="D82">
-        <v>97.80522456334916</v>
+        <v>96.76143831118267</v>
       </c>
       <c r="E82">
-        <v>392.66</v>
+        <v>398.222</v>
       </c>
       <c r="F82">
-        <v>444.96</v>
+        <v>450.522</v>
       </c>
       <c r="G82">
         <v>35.3</v>
@@ -8139,37 +8139,37 @@
         <v>23.2</v>
       </c>
       <c r="M82">
-        <v>104.921568</v>
+        <v>106.2330876</v>
       </c>
       <c r="N82">
-        <v>-81.72156799999999</v>
+        <v>-83.0330876</v>
       </c>
       <c r="O82">
-        <v>-16.3443136</v>
+        <v>-16.60661752</v>
       </c>
       <c r="P82">
-        <v>-65.3772544</v>
+        <v>-66.42647008</v>
       </c>
       <c r="Q82">
-        <v>-55.2772544</v>
+        <v>-56.32647008000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2081839380495885</v>
+        <v>0.21673046110483</v>
       </c>
       <c r="T82">
-        <v>3.16516519765143</v>
+        <v>3.331752839633085</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.0442235098888343</v>
+        <v>0.04367754063094745</v>
       </c>
       <c r="W82">
-        <v>0.2253720963682129</v>
+        <v>0.2255008359192226</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2211175494441715</v>
+        <v>0.2183877031547373</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8185,22 +8185,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.223834464704488</v>
+        <v>0.225734464704488</v>
       </c>
       <c r="C83">
-        <v>-318.4605616888173</v>
+        <v>-325.0443044277261</v>
       </c>
       <c r="D83">
-        <v>96.76143831118267</v>
+        <v>95.73969557227392</v>
       </c>
       <c r="E83">
-        <v>398.222</v>
+        <v>403.784</v>
       </c>
       <c r="F83">
-        <v>450.522</v>
+        <v>456.084</v>
       </c>
       <c r="G83">
         <v>35.3</v>
@@ -8221,37 +8221,37 @@
         <v>23.2</v>
       </c>
       <c r="M83">
-        <v>106.2330876</v>
+        <v>107.5446072</v>
       </c>
       <c r="N83">
-        <v>-83.0330876</v>
+        <v>-84.3446072</v>
       </c>
       <c r="O83">
-        <v>-16.60661752</v>
+        <v>-16.86892144</v>
       </c>
       <c r="P83">
-        <v>-66.42647008</v>
+        <v>-67.47568576</v>
       </c>
       <c r="Q83">
-        <v>-56.32647008000001</v>
+        <v>-57.37568576000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.21673046110483</v>
+        <v>0.2262265978328761</v>
       </c>
       <c r="T83">
-        <v>3.331752839633085</v>
+        <v>3.5168502196127</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.04367754063094745</v>
+        <v>0.0431448876964237</v>
       </c>
       <c r="W83">
-        <v>0.2255008359192226</v>
+        <v>0.2256264354811833</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2183877031547373</v>
+        <v>0.2157244384821185</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8267,22 +8267,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.225734464704488</v>
+        <v>0.227634464704488</v>
       </c>
       <c r="C84">
-        <v>-325.0443044277261</v>
+        <v>-331.6066946556344</v>
       </c>
       <c r="D84">
-        <v>95.73969557227392</v>
+        <v>94.73930534436555</v>
       </c>
       <c r="E84">
-        <v>403.784</v>
+        <v>409.3459999999999</v>
       </c>
       <c r="F84">
-        <v>456.084</v>
+        <v>461.646</v>
       </c>
       <c r="G84">
         <v>35.3</v>
@@ -8303,37 +8303,37 @@
         <v>23.2</v>
       </c>
       <c r="M84">
-        <v>107.5446072</v>
+        <v>108.8561268</v>
       </c>
       <c r="N84">
-        <v>-84.3446072</v>
+        <v>-85.6561268</v>
       </c>
       <c r="O84">
-        <v>-16.86892144</v>
+        <v>-17.13122536</v>
       </c>
       <c r="P84">
-        <v>-67.47568576</v>
+        <v>-68.52490143999999</v>
       </c>
       <c r="Q84">
-        <v>-57.37568576000001</v>
+        <v>-58.42490144</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2262265978328761</v>
+        <v>0.236839927117163</v>
       </c>
       <c r="T84">
-        <v>3.5168502196127</v>
+        <v>3.723723761942859</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.0431448876964237</v>
+        <v>0.04262506977237041</v>
       </c>
       <c r="W84">
-        <v>0.2256264354811833</v>
+        <v>0.225749008547675</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2157244384821185</v>
+        <v>0.2131253488618521</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8349,22 +8349,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.227634464704488</v>
+        <v>0.229534464704488</v>
       </c>
       <c r="C85">
-        <v>-331.6066946556344</v>
+        <v>-338.1483947921537</v>
       </c>
       <c r="D85">
-        <v>94.73930534436555</v>
+        <v>93.75960520784622</v>
       </c>
       <c r="E85">
-        <v>409.3459999999999</v>
+        <v>414.908</v>
       </c>
       <c r="F85">
-        <v>461.646</v>
+        <v>467.208</v>
       </c>
       <c r="G85">
         <v>35.3</v>
@@ -8385,37 +8385,37 @@
         <v>23.2</v>
       </c>
       <c r="M85">
-        <v>108.8561268</v>
+        <v>110.1676464</v>
       </c>
       <c r="N85">
-        <v>-85.6561268</v>
+        <v>-86.96764639999999</v>
       </c>
       <c r="O85">
-        <v>-17.13122536</v>
+        <v>-17.39352928</v>
       </c>
       <c r="P85">
-        <v>-68.52490143999999</v>
+        <v>-69.57411712</v>
       </c>
       <c r="Q85">
-        <v>-58.42490144</v>
+        <v>-59.47411712</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.236839927117163</v>
+        <v>0.2487799225619857</v>
       </c>
       <c r="T85">
-        <v>3.723723761942859</v>
+        <v>3.956456497064289</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.04262506977237041</v>
+        <v>0.04211762846555647</v>
       </c>
       <c r="W85">
-        <v>0.225749008547675</v>
+        <v>0.2258686632078218</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2131253488618521</v>
+        <v>0.2105881423277824</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8431,22 +8431,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.229534464704488</v>
+        <v>0.231434464704488</v>
       </c>
       <c r="C86">
-        <v>-338.1483947921537</v>
+        <v>-344.6700401369903</v>
       </c>
       <c r="D86">
-        <v>93.75960520784622</v>
+        <v>92.79995986300958</v>
       </c>
       <c r="E86">
-        <v>414.9079999999999</v>
+        <v>420.4699999999999</v>
       </c>
       <c r="F86">
-        <v>467.2079999999999</v>
+        <v>472.7699999999999</v>
       </c>
       <c r="G86">
         <v>35.3</v>
@@ -8467,37 +8467,37 @@
         <v>23.2</v>
       </c>
       <c r="M86">
-        <v>110.1676464</v>
+        <v>111.479166</v>
       </c>
       <c r="N86">
-        <v>-86.96764639999998</v>
+        <v>-88.27916599999999</v>
       </c>
       <c r="O86">
-        <v>-17.39352928</v>
+        <v>-17.6558332</v>
       </c>
       <c r="P86">
-        <v>-69.57411711999998</v>
+        <v>-70.62333279999999</v>
       </c>
       <c r="Q86">
-        <v>-59.47411711999999</v>
+        <v>-60.52333279999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2487799225619856</v>
+        <v>0.2623119173994513</v>
       </c>
       <c r="T86">
-        <v>3.956456497064286</v>
+        <v>4.220220263535238</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.04211762846555648</v>
+        <v>0.04162212695419699</v>
       </c>
       <c r="W86">
-        <v>0.2258686632078218</v>
+        <v>0.2259855024642003</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2105881423277824</v>
+        <v>0.208110634770985</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8513,22 +8513,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.231434464704488</v>
+        <v>0.233334464704488</v>
       </c>
       <c r="C87">
-        <v>-344.6700401369903</v>
+        <v>-351.1722402437684</v>
       </c>
       <c r="D87">
-        <v>92.79995986300958</v>
+        <v>91.85975975623155</v>
       </c>
       <c r="E87">
-        <v>420.4699999999999</v>
+        <v>426.0319999999999</v>
       </c>
       <c r="F87">
-        <v>472.7699999999999</v>
+        <v>478.3319999999999</v>
       </c>
       <c r="G87">
         <v>35.3</v>
@@ -8549,37 +8549,37 @@
         <v>23.2</v>
       </c>
       <c r="M87">
-        <v>111.479166</v>
+        <v>112.7906856</v>
       </c>
       <c r="N87">
-        <v>-88.27916599999999</v>
+        <v>-89.59068559999999</v>
       </c>
       <c r="O87">
-        <v>-17.6558332</v>
+        <v>-17.91813712</v>
       </c>
       <c r="P87">
-        <v>-70.62333279999999</v>
+        <v>-71.67254847999999</v>
       </c>
       <c r="Q87">
-        <v>-60.52333279999999</v>
+        <v>-61.57254847999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2623119173994513</v>
+        <v>0.277777054356555</v>
       </c>
       <c r="T87">
-        <v>4.220220263535238</v>
+        <v>4.52166456807347</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.04162212695419699</v>
+        <v>0.04113814873379935</v>
       </c>
       <c r="W87">
-        <v>0.2259855024642003</v>
+        <v>0.2260996245285701</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8587,7 +8587,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.208110634770985</v>
+        <v>0.2056907436689968</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8595,22 +8595,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.233334464704488</v>
+        <v>0.235234464704488</v>
       </c>
       <c r="C88">
-        <v>-351.1722402437684</v>
+        <v>-357.6555802111767</v>
       </c>
       <c r="D88">
-        <v>91.85975975623155</v>
+        <v>90.93841978882324</v>
       </c>
       <c r="E88">
-        <v>426.0319999999999</v>
+        <v>431.5939999999999</v>
       </c>
       <c r="F88">
-        <v>478.3319999999999</v>
+        <v>483.8939999999999</v>
       </c>
       <c r="G88">
         <v>35.3</v>
@@ -8631,37 +8631,37 @@
         <v>23.2</v>
       </c>
       <c r="M88">
-        <v>112.7906856</v>
+        <v>114.1022052</v>
       </c>
       <c r="N88">
-        <v>-89.59068559999999</v>
+        <v>-90.90220519999998</v>
       </c>
       <c r="O88">
-        <v>-17.91813712</v>
+        <v>-18.18044104</v>
       </c>
       <c r="P88">
-        <v>-71.67254847999999</v>
+        <v>-72.72176415999999</v>
       </c>
       <c r="Q88">
-        <v>-61.57254847999999</v>
+        <v>-62.62176416</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.277777054356555</v>
+        <v>0.295621443153213</v>
       </c>
       <c r="T88">
-        <v>4.52166456807347</v>
+        <v>4.869484919463737</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.04113814873379935</v>
+        <v>0.04066529644950281</v>
       </c>
       <c r="W88">
-        <v>0.2260996245285701</v>
+        <v>0.2262111230972073</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2056907436689968</v>
+        <v>0.203326482247514</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8677,22 +8677,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.235234464704488</v>
+        <v>0.237134464704488</v>
       </c>
       <c r="C89">
-        <v>-357.6555802111767</v>
+        <v>-364.1206218971878</v>
       </c>
       <c r="D89">
-        <v>90.93841978882324</v>
+        <v>90.03537810281219</v>
       </c>
       <c r="E89">
-        <v>431.5939999999999</v>
+        <v>437.1559999999999</v>
       </c>
       <c r="F89">
-        <v>483.8939999999999</v>
+        <v>489.456</v>
       </c>
       <c r="G89">
         <v>35.3</v>
@@ -8713,37 +8713,37 @@
         <v>23.2</v>
       </c>
       <c r="M89">
-        <v>114.1022052</v>
+        <v>115.4137248</v>
       </c>
       <c r="N89">
-        <v>-90.90220519999998</v>
+        <v>-92.21372479999999</v>
       </c>
       <c r="O89">
-        <v>-18.18044104</v>
+        <v>-18.44274496</v>
       </c>
       <c r="P89">
-        <v>-72.72176415999999</v>
+        <v>-73.77097984</v>
       </c>
       <c r="Q89">
-        <v>-62.62176416</v>
+        <v>-63.67097984</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.295621443153213</v>
+        <v>0.3164398967493142</v>
       </c>
       <c r="T89">
-        <v>4.869484919463737</v>
+        <v>5.275275329419049</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.04066529644950281</v>
+        <v>0.04020319080803118</v>
       </c>
       <c r="W89">
-        <v>0.2262111230972073</v>
+        <v>0.2263200876074663</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.203326482247514</v>
+        <v>0.2010159540401559</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8759,22 +8759,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.237134464704488</v>
+        <v>0.239034464704488</v>
       </c>
       <c r="C90">
-        <v>-364.1206218971878</v>
+        <v>-370.5679050616427</v>
       </c>
       <c r="D90">
-        <v>90.03537810281219</v>
+        <v>89.15009493835726</v>
       </c>
       <c r="E90">
-        <v>437.1559999999999</v>
+        <v>442.718</v>
       </c>
       <c r="F90">
-        <v>489.456</v>
+        <v>495.018</v>
       </c>
       <c r="G90">
         <v>35.3</v>
@@ -8795,37 +8795,37 @@
         <v>23.2</v>
       </c>
       <c r="M90">
-        <v>115.4137248</v>
+        <v>116.7252444</v>
       </c>
       <c r="N90">
-        <v>-92.21372479999999</v>
+        <v>-93.52524439999999</v>
       </c>
       <c r="O90">
-        <v>-18.44274496</v>
+        <v>-18.70504888</v>
       </c>
       <c r="P90">
-        <v>-73.77097984</v>
+        <v>-74.82019552</v>
       </c>
       <c r="Q90">
-        <v>-63.67097984</v>
+        <v>-64.72019552</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3164398967493142</v>
+        <v>0.3410435237265245</v>
       </c>
       <c r="T90">
-        <v>5.275275329419049</v>
+        <v>5.75484581391169</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.04020319080803118</v>
+        <v>0.03975146956299713</v>
       </c>
       <c r="W90">
-        <v>0.2263200876074663</v>
+        <v>0.2264266034770453</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2010159540401559</v>
+        <v>0.1987573478149857</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8841,22 +8841,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.239034464704488</v>
+        <v>0.240934464704488</v>
       </c>
       <c r="C91">
-        <v>-370.5679050616427</v>
+        <v>-376.997948442085</v>
       </c>
       <c r="D91">
-        <v>89.15009493835726</v>
+        <v>88.28205155791495</v>
       </c>
       <c r="E91">
-        <v>442.718</v>
+        <v>448.2799999999999</v>
       </c>
       <c r="F91">
-        <v>495.018</v>
+        <v>500.5799999999999</v>
       </c>
       <c r="G91">
         <v>35.3</v>
@@ -8877,37 +8877,37 @@
         <v>23.2</v>
       </c>
       <c r="M91">
-        <v>116.7252444</v>
+        <v>118.036764</v>
       </c>
       <c r="N91">
-        <v>-93.52524439999999</v>
+        <v>-94.83676399999999</v>
       </c>
       <c r="O91">
-        <v>-18.70504888</v>
+        <v>-18.9673528</v>
       </c>
       <c r="P91">
-        <v>-74.82019552</v>
+        <v>-75.86941119999999</v>
       </c>
       <c r="Q91">
-        <v>-64.72019552</v>
+        <v>-65.76941119999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3410435237265245</v>
+        <v>0.3705678760991771</v>
       </c>
       <c r="T91">
-        <v>5.75484581391169</v>
+        <v>6.330330395302861</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.03975146956299713</v>
+        <v>0.03930978656785272</v>
       </c>
       <c r="W91">
-        <v>0.2264266034770453</v>
+        <v>0.2265307523273004</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1987573478149857</v>
+        <v>0.1965489328392636</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8923,22 +8923,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.240934464704488</v>
+        <v>0.242834464704488</v>
       </c>
       <c r="C92">
-        <v>-376.997948442085</v>
+        <v>-383.4112507673487</v>
       </c>
       <c r="D92">
-        <v>88.28205155791495</v>
+        <v>87.43074923265119</v>
       </c>
       <c r="E92">
-        <v>448.2799999999999</v>
+        <v>453.8419999999999</v>
       </c>
       <c r="F92">
-        <v>500.5799999999999</v>
+        <v>506.1419999999999</v>
       </c>
       <c r="G92">
         <v>35.3</v>
@@ -8959,37 +8959,37 @@
         <v>23.2</v>
       </c>
       <c r="M92">
-        <v>118.036764</v>
+        <v>119.3482836</v>
       </c>
       <c r="N92">
-        <v>-94.83676399999999</v>
+        <v>-96.14828359999998</v>
       </c>
       <c r="O92">
-        <v>-18.9673528</v>
+        <v>-19.22965672</v>
       </c>
       <c r="P92">
-        <v>-75.86941119999999</v>
+        <v>-76.91862687999999</v>
       </c>
       <c r="Q92">
-        <v>-65.76941119999999</v>
+        <v>-66.81862688</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3705678760991771</v>
+        <v>0.4066531956657523</v>
       </c>
       <c r="T92">
-        <v>6.330330395302861</v>
+        <v>7.033700439225401</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03930978656785272</v>
+        <v>0.0388778108912829</v>
       </c>
       <c r="W92">
-        <v>0.2265307523273004</v>
+        <v>0.2266326121918355</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1965489328392636</v>
+        <v>0.1943890544564145</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9005,22 +9005,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.242834464704488</v>
+        <v>0.244734464704488</v>
       </c>
       <c r="C93">
-        <v>-383.4112507673487</v>
+        <v>-389.8082917130632</v>
       </c>
       <c r="D93">
-        <v>87.43074923265119</v>
+        <v>86.5957082869367</v>
       </c>
       <c r="E93">
-        <v>453.8419999999999</v>
+        <v>459.4039999999999</v>
       </c>
       <c r="F93">
-        <v>506.1419999999999</v>
+        <v>511.704</v>
       </c>
       <c r="G93">
         <v>35.3</v>
@@ -9041,37 +9041,37 @@
         <v>23.2</v>
       </c>
       <c r="M93">
-        <v>119.3482836</v>
+        <v>120.6598032</v>
       </c>
       <c r="N93">
-        <v>-96.14828359999998</v>
+        <v>-97.4598032</v>
       </c>
       <c r="O93">
-        <v>-19.22965672</v>
+        <v>-19.49196064</v>
       </c>
       <c r="P93">
-        <v>-76.91862687999999</v>
+        <v>-77.96784255999999</v>
       </c>
       <c r="Q93">
-        <v>-66.81862688</v>
+        <v>-67.86784256</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4066531956657523</v>
+        <v>0.4517598451239714</v>
       </c>
       <c r="T93">
-        <v>7.033700439225401</v>
+        <v>7.912912994128578</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.0388778108912829</v>
+        <v>0.03845522599029069</v>
       </c>
       <c r="W93">
-        <v>0.2266326121918355</v>
+        <v>0.2267322577114895</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1943890544564145</v>
+        <v>0.1922761299514535</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9087,22 +9087,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.244734464704488</v>
+        <v>0.246634464704488</v>
       </c>
       <c r="C94">
-        <v>-389.8082917130632</v>
+        <v>-396.1895328029194</v>
       </c>
       <c r="D94">
-        <v>86.5957082869367</v>
+        <v>85.77646719708055</v>
       </c>
       <c r="E94">
-        <v>459.4039999999999</v>
+        <v>464.966</v>
       </c>
       <c r="F94">
-        <v>511.704</v>
+        <v>517.266</v>
       </c>
       <c r="G94">
         <v>35.3</v>
@@ -9123,37 +9123,37 @@
         <v>23.2</v>
       </c>
       <c r="M94">
-        <v>120.6598032</v>
+        <v>121.9713228</v>
       </c>
       <c r="N94">
-        <v>-97.4598032</v>
+        <v>-98.77132279999999</v>
       </c>
       <c r="O94">
-        <v>-19.49196064</v>
+        <v>-19.75426456</v>
       </c>
       <c r="P94">
-        <v>-77.96784255999999</v>
+        <v>-79.01705824</v>
       </c>
       <c r="Q94">
-        <v>-67.86784256</v>
+        <v>-68.91705824</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4517598451239714</v>
+        <v>0.5097541087131102</v>
       </c>
       <c r="T94">
-        <v>7.912912994128578</v>
+        <v>9.043329136146948</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03845522599029069</v>
+        <v>0.03804172893663166</v>
       </c>
       <c r="W94">
-        <v>0.2267322577114895</v>
+        <v>0.2268297603167423</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1922761299514535</v>
+        <v>0.1902086446831583</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9169,22 +9169,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.246634464704488</v>
+        <v>0.248534464704488</v>
       </c>
       <c r="C95">
-        <v>-396.1895328029194</v>
+        <v>-402.5554182592576</v>
       </c>
       <c r="D95">
-        <v>85.77646719708055</v>
+        <v>84.97258174074236</v>
       </c>
       <c r="E95">
-        <v>464.966</v>
+        <v>470.528</v>
       </c>
       <c r="F95">
-        <v>517.266</v>
+        <v>522.828</v>
       </c>
       <c r="G95">
         <v>35.3</v>
@@ -9205,37 +9205,37 @@
         <v>23.2</v>
       </c>
       <c r="M95">
-        <v>121.9713228</v>
+        <v>123.2828424</v>
       </c>
       <c r="N95">
-        <v>-98.77132279999999</v>
+        <v>-100.0828424</v>
       </c>
       <c r="O95">
-        <v>-19.75426456</v>
+        <v>-20.01656848</v>
       </c>
       <c r="P95">
-        <v>-79.01705824</v>
+        <v>-80.06627391999999</v>
       </c>
       <c r="Q95">
-        <v>-68.91705824</v>
+        <v>-69.96627391999999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5097541087131102</v>
+        <v>0.5870797934986287</v>
       </c>
       <c r="T95">
-        <v>9.043329136146948</v>
+        <v>10.55055065883811</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03804172893663166</v>
+        <v>0.03763702969262494</v>
       </c>
       <c r="W95">
-        <v>0.2268297603167423</v>
+        <v>0.2269251883984791</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1902086446831583</v>
+        <v>0.1881851484631247</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9251,22 +9251,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.248534464704488</v>
+        <v>0.250434464704488</v>
       </c>
       <c r="C96">
-        <v>-402.5554182592576</v>
+        <v>-408.9063758062699</v>
       </c>
       <c r="D96">
-        <v>84.97258174074236</v>
+        <v>84.1836241937301</v>
       </c>
       <c r="E96">
-        <v>470.528</v>
+        <v>476.09</v>
       </c>
       <c r="F96">
-        <v>522.828</v>
+        <v>528.39</v>
       </c>
       <c r="G96">
         <v>35.3</v>
@@ -9287,37 +9287,37 @@
         <v>23.2</v>
       </c>
       <c r="M96">
-        <v>123.2828424</v>
+        <v>124.594362</v>
       </c>
       <c r="N96">
-        <v>-100.0828424</v>
+        <v>-101.394362</v>
       </c>
       <c r="O96">
-        <v>-20.01656848</v>
+        <v>-20.2788724</v>
       </c>
       <c r="P96">
-        <v>-80.06627391999999</v>
+        <v>-81.1154896</v>
       </c>
       <c r="Q96">
-        <v>-69.96627391999999</v>
+        <v>-71.01548960000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5870797934986287</v>
+        <v>0.6953357521983548</v>
       </c>
       <c r="T96">
-        <v>10.55055065883811</v>
+        <v>12.66066079060574</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03763702969262494</v>
+        <v>0.03724085043270256</v>
       </c>
       <c r="W96">
-        <v>0.2269251883984791</v>
+        <v>0.2270186074679688</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1881851484631247</v>
+        <v>0.1862042521635129</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9333,22 +9333,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.250434464704488</v>
+        <v>0.252334464704488</v>
       </c>
       <c r="C97">
-        <v>-408.9063758062699</v>
+        <v>-415.2428174288676</v>
       </c>
       <c r="D97">
-        <v>84.1836241937301</v>
+        <v>83.40918257113245</v>
       </c>
       <c r="E97">
-        <v>476.09</v>
+        <v>481.652</v>
       </c>
       <c r="F97">
-        <v>528.39</v>
+        <v>533.952</v>
       </c>
       <c r="G97">
         <v>35.3</v>
@@ -9369,37 +9369,37 @@
         <v>23.2</v>
       </c>
       <c r="M97">
-        <v>124.594362</v>
+        <v>125.9058816</v>
       </c>
       <c r="N97">
-        <v>-101.394362</v>
+        <v>-102.7058816</v>
       </c>
       <c r="O97">
-        <v>-20.2788724</v>
+        <v>-20.54117632</v>
       </c>
       <c r="P97">
-        <v>-81.1154896</v>
+        <v>-82.16470527999999</v>
       </c>
       <c r="Q97">
-        <v>-71.01548960000001</v>
+        <v>-72.06470528</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6953357521983548</v>
+        <v>0.8577196902479439</v>
       </c>
       <c r="T97">
-        <v>12.66066079060574</v>
+        <v>15.82582598825718</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03724085043270256</v>
+        <v>0.03685292490736191</v>
       </c>
       <c r="W97">
-        <v>0.2270186074679688</v>
+        <v>0.2271100803068441</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1862042521635129</v>
+        <v>0.1842646245368096</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9415,22 +9415,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.252334464704488</v>
+        <v>0.254234464704488</v>
       </c>
       <c r="C98">
-        <v>-415.2428174288675</v>
+        <v>-421.5651400900446</v>
       </c>
       <c r="D98">
-        <v>83.40918257113245</v>
+        <v>82.64885990995531</v>
       </c>
       <c r="E98">
-        <v>481.6519999999999</v>
+        <v>487.2139999999999</v>
       </c>
       <c r="F98">
-        <v>533.9519999999999</v>
+        <v>539.5139999999999</v>
       </c>
       <c r="G98">
         <v>35.3</v>
@@ -9451,37 +9451,37 @@
         <v>23.2</v>
       </c>
       <c r="M98">
-        <v>125.9058816</v>
+        <v>127.2174012</v>
       </c>
       <c r="N98">
-        <v>-102.7058816</v>
+        <v>-104.0174012</v>
       </c>
       <c r="O98">
-        <v>-20.54117631999999</v>
+        <v>-20.80348024</v>
       </c>
       <c r="P98">
-        <v>-82.16470527999998</v>
+        <v>-83.21392095999998</v>
       </c>
       <c r="Q98">
-        <v>-72.06470527999998</v>
+        <v>-73.11392095999999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8577196902479416</v>
+        <v>1.128359586997256</v>
       </c>
       <c r="T98">
-        <v>15.82582598825713</v>
+        <v>21.10110131767618</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.03685292490736192</v>
+        <v>0.03647299784646128</v>
       </c>
       <c r="W98">
-        <v>0.2271100803068441</v>
+        <v>0.2271996671078044</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9489,7 +9489,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1842646245368096</v>
+        <v>0.1823649892323064</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9497,22 +9497,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.254234464704488</v>
+        <v>0.256134464704488</v>
       </c>
       <c r="C99">
-        <v>-421.5651400900446</v>
+        <v>-427.8737264093601</v>
       </c>
       <c r="D99">
-        <v>82.64885990995531</v>
+        <v>81.90227359063984</v>
       </c>
       <c r="E99">
-        <v>487.2139999999999</v>
+        <v>492.7759999999999</v>
       </c>
       <c r="F99">
-        <v>539.5139999999999</v>
+        <v>545.0759999999999</v>
       </c>
       <c r="G99">
         <v>35.3</v>
@@ -9533,37 +9533,37 @@
         <v>23.2</v>
       </c>
       <c r="M99">
-        <v>127.2174012</v>
+        <v>128.5289208</v>
       </c>
       <c r="N99">
-        <v>-104.0174012</v>
+        <v>-105.3289208</v>
       </c>
       <c r="O99">
-        <v>-20.80348024</v>
+        <v>-21.06578416</v>
       </c>
       <c r="P99">
-        <v>-83.21392095999998</v>
+        <v>-84.26313663999998</v>
       </c>
       <c r="Q99">
-        <v>-73.11392095999999</v>
+        <v>-74.16313663999999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.128359586997256</v>
+        <v>1.669639380495883</v>
       </c>
       <c r="T99">
-        <v>21.10110131767618</v>
+        <v>31.65165197651427</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.03647299784646128</v>
+        <v>0.03610082439904841</v>
       </c>
       <c r="W99">
-        <v>0.2271996671078044</v>
+        <v>0.2272874256067044</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1823649892323064</v>
+        <v>0.1805041219952421</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9579,22 +9579,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.256134464704488</v>
+        <v>0.258034464704488</v>
       </c>
       <c r="C100">
-        <v>-427.8737264093601</v>
+        <v>-434.1689453049758</v>
       </c>
       <c r="D100">
-        <v>81.90227359063984</v>
+        <v>81.1690546950241</v>
       </c>
       <c r="E100">
-        <v>492.7759999999999</v>
+        <v>498.3379999999999</v>
       </c>
       <c r="F100">
-        <v>545.0759999999999</v>
+        <v>550.6379999999999</v>
       </c>
       <c r="G100">
         <v>35.3</v>
@@ -9615,37 +9615,37 @@
         <v>23.2</v>
       </c>
       <c r="M100">
-        <v>128.5289208</v>
+        <v>129.8404404</v>
       </c>
       <c r="N100">
-        <v>-105.3289208</v>
+        <v>-106.6404404</v>
       </c>
       <c r="O100">
-        <v>-21.06578416</v>
+        <v>-21.32808808</v>
       </c>
       <c r="P100">
-        <v>-84.26313663999998</v>
+        <v>-85.31235231999997</v>
       </c>
       <c r="Q100">
-        <v>-74.16313663999999</v>
+        <v>-75.21235231999998</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.669639380495883</v>
+        <v>3.293478760991766</v>
       </c>
       <c r="T100">
-        <v>31.65165197651427</v>
+        <v>63.30330395302853</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.03610082439904841</v>
+        <v>0.03573616960713883</v>
       </c>
       <c r="W100">
-        <v>0.2272874256067044</v>
+        <v>0.2273734112066366</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9653,91 +9653,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1805041219952421</v>
+        <v>0.1786808480356942</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.258034464704488</v>
-      </c>
-      <c r="C101">
-        <v>-434.1689453049758</v>
-      </c>
-      <c r="D101">
-        <v>81.1690546950241</v>
-      </c>
-      <c r="E101">
-        <v>498.3379999999999</v>
-      </c>
-      <c r="F101">
-        <v>550.6379999999999</v>
-      </c>
-      <c r="G101">
-        <v>35.3</v>
-      </c>
-      <c r="H101">
-        <v>503.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>33.3</v>
-      </c>
-      <c r="K101">
-        <v>10.1</v>
-      </c>
-      <c r="L101">
-        <v>23.2</v>
-      </c>
-      <c r="M101">
-        <v>129.8404404</v>
-      </c>
-      <c r="N101">
-        <v>-106.6404404</v>
-      </c>
-      <c r="O101">
-        <v>-21.32808808</v>
-      </c>
-      <c r="P101">
-        <v>-85.31235231999997</v>
-      </c>
-      <c r="Q101">
-        <v>-75.21235231999998</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.293478760991766</v>
-      </c>
-      <c r="T101">
-        <v>63.30330395302853</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.03573616960713883</v>
-      </c>
-      <c r="W101">
-        <v>0.2273734112066366</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1786808480356942</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
